--- a/outputs/rapport_chiffre_affaires.xlsx
+++ b/outputs/rapport_chiffre_affaires.xlsx
@@ -1803,19 +1803,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Domaine de Vaccelli AOP Ajaccio Rouge Granit 2016</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2015</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>230</v>
@@ -1824,19 +1824,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2015</t>
+          <t>Domaine de Vaccelli AOP Ajaccio Rouge Granit 2016</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
         <v>230</v>
@@ -2370,19 +2370,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Domaine de l'Hortus Pic Saint-Loup La Grande Cuvée 2018</t>
+          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge La Grande Pièce 2013</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
         <v>168</v>
@@ -2391,12 +2391,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Sancerre Blanc La Moussière 2018</t>
+          <t>Domaine de l'Hortus Pic Saint-Loup La Grande Cuvée 2018</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2412,19 +2412,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge La Grande Pièce 2013</t>
+          <t>Alphonse Mellot Sancerre Blanc La Moussière 2018</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
         <v>168</v>
@@ -2475,19 +2475,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Elian Daros Côtes du Marmandais Abouriou 2016</t>
+          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2007</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>13.7</v>
+        <v>54.8</v>
       </c>
       <c r="D98" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
         <v>164.4</v>
@@ -2496,19 +2496,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2007</t>
+          <t>Elian Daros Côtes du Marmandais Abouriou 2016</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>54.8</v>
+        <v>13.7</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E99" t="n">
         <v>164.4</v>
@@ -2517,19 +2517,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gilles Robin Crozes-Hermitage Blanc Les Marelles 2018</t>
+          <t>David Duband Côtes de Nuits Villages 2017</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>23.4</v>
+        <v>27.3</v>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
         <v>163.8</v>
@@ -2538,19 +2538,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>David Duband Côtes de Nuits Villages 2017</t>
+          <t>Gilles Robin Crozes-Hermitage Blanc Les Marelles 2018</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>27.3</v>
+        <v>23.4</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
         <v>163.8</v>
@@ -3147,19 +3147,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Domaine Pellé Sancerre Blanc La Croix Au Garde 2018</t>
+          <t>Gilbert Picq Chablis 1er Cru Vaucoupin 2016</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>19</v>
+        <v>26.6</v>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
         <v>133</v>
@@ -3168,19 +3168,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gilbert Picq Chablis 1er Cru Vaucoupin 2016</t>
+          <t>Domaine Pellé Sancerre Blanc La Croix Au Garde 2018</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>26.6</v>
+        <v>19</v>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" t="n">
         <v>133</v>
@@ -3399,19 +3399,19 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Elian Daros Côtes du Marmandais Coucou Blanc 2016</t>
+          <t>Domaine Rouge Garance Côtes du Rhône Blanc De Garance 2018</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>20.35</v>
+        <v>11.1</v>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E142" t="n">
         <v>122.1</v>
@@ -3420,19 +3420,19 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Domaine Rouge Garance Côtes du Rhône Blanc De Garance 2018</t>
+          <t>Elian Daros Côtes du Marmandais Coucou Blanc 2016</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>11.1</v>
+        <v>20.35</v>
       </c>
       <c r="D143" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E143" t="n">
         <v>122.1</v>
@@ -3525,19 +3525,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Philippe Nusswitz Duché d'Uzès Orénia Blanc 2018</t>
+          <t>David Duband Vosne Romanée 2017</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>9.9</v>
+        <v>59.4</v>
       </c>
       <c r="D148" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
         <v>118.8</v>
@@ -3546,19 +3546,19 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>David Duband Vosne Romanée 2017</t>
+          <t>Philippe Nusswitz Duché d'Uzès Orénia Blanc 2018</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>59.4</v>
+        <v>9.9</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E149" t="n">
         <v>118.8</v>
@@ -3735,19 +3735,19 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Domaine des Terres d'Ocre Saint-Pourçain Rouge Instant T 2015</t>
+          <t>Château de La Liquière Faugères Cistus Blanc 2019</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="D158" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E158" t="n">
         <v>108</v>
@@ -3777,19 +3777,19 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Château de La Liquière Faugères Cistus Blanc 2019</t>
+          <t>Domaine des Terres d'Ocre Saint-Pourçain Rouge Instant T 2015</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="D160" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E160" t="n">
         <v>108</v>
@@ -3819,19 +3819,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Domaine Saint-Denis Mâcon Lugny 2017</t>
+          <t>Borie La Vitarèle Saint-Chinian Les Terres Blanches 2019</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>15.3</v>
+        <v>11.9</v>
       </c>
       <c r="D162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E162" t="n">
         <v>107.1</v>
@@ -3840,19 +3840,19 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Borie La Vitarèle Saint-Chinian Les Terres Blanches 2019</t>
+          <t>Domaine Saint-Denis Mâcon Lugny 2017</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>11.9</v>
+        <v>15.3</v>
       </c>
       <c r="D163" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E163" t="n">
         <v>107.1</v>
@@ -4008,19 +4008,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Champagne Mailly Grand Cru Extra Brut Millésimé 2012</t>
+          <t>Triennes IGP Méditerranée Rouge Les Auréliens 2016</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E171" t="n">
         <v>99</v>
@@ -4029,19 +4029,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Triennes IGP Méditerranée Rouge Les Auréliens 2016</t>
+          <t>Champagne Mailly Grand Cru Extra Brut Millésimé 2012</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D172" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E172" t="n">
         <v>99</v>
@@ -4659,12 +4659,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>La Cotelleraie Saint-Nicolas-de-Bourgueil La Croisée 2018</t>
+          <t>Emile Boeckel Pinot Noir Barriques Oberpfoeller 2018</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -4680,12 +4680,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Emile Boeckel Pinot Noir Barriques Oberpfoeller 2018</t>
+          <t>La Cotelleraie Saint-Nicolas-de-Bourgueil La Croisée 2018</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5037,19 +5037,19 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Domaine Weinbach Riesling Grand Cru Schlossberg Cuvée Ste Catherine 2018</t>
+          <t>Zind-Humbrecht Riesling Herrenweg de Turckheim 2017</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>63.4</v>
+        <v>31.7</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E220" t="n">
         <v>63.4</v>
@@ -5058,19 +5058,19 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Riesling Herrenweg de Turckheim 2017</t>
+          <t>Domaine Weinbach Riesling Grand Cru Schlossberg Cuvée Ste Catherine 2018</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>31.7</v>
+        <v>63.4</v>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E221" t="n">
         <v>63.4</v>
@@ -5226,12 +5226,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mas Laval IGP Pays d'Hérault Les Pampres Blancs 2018</t>
+          <t>Clos du Mont-Olivet Vins de Pays du Gard Rive Droite 2018</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -5247,12 +5247,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Vins de Pays du Gard Rive Droite 2018</t>
+          <t>Mas Laval IGP Pays d'Hérault Les Pampres Blancs 2018</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -5289,19 +5289,19 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Maurice Schoech Gewurztraminer Vendanges Tardives 2017</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Spice King Batch Strength</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>29.5</v>
+        <v>59</v>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E232" t="n">
         <v>59</v>
@@ -5310,19 +5310,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Spice King Batch Strength</t>
+          <t>Maurice Schoech Gewurztraminer Vendanges Tardives 2017</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>59</v>
+        <v>29.5</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
         <v>59</v>
@@ -5688,19 +5688,19 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Catherine et Claude Maréchal Volnay 2017</t>
+          <t>Borie La Vitarèle Saint-Chinian Les Schistes 2017</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>50.1</v>
+        <v>16.7</v>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E251" t="n">
         <v>50.1</v>
@@ -5709,19 +5709,19 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Borie La Vitarèle Saint-Chinian Les Schistes 2017</t>
+          <t>Catherine et Claude Maréchal Volnay 2017</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>16.7</v>
+        <v>50.1</v>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E252" t="n">
         <v>50.1</v>
@@ -5982,19 +5982,19 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jeanne Gaillard IGP Collines Rhodaniennes Syrah Terre de Mandrin 2018</t>
+          <t>Emile Boeckel Crémant Chardonnay Extra Brut 2016</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="D265" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E265" t="n">
         <v>46.2</v>
@@ -6003,19 +6003,19 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Emile Boeckel Crémant Chardonnay Extra Brut 2016</t>
+          <t>Jeanne Gaillard IGP Collines Rhodaniennes Syrah Terre de Mandrin 2018</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E266" t="n">
         <v>46.2</v>
@@ -6612,12 +6612,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Xavier Frissant Touraine Amboise L'Orée des Frênes 2015</t>
+          <t>Maurice Schoech Pinot Gris 2018</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -6633,12 +6633,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Maurice Schoech Pinot Gris 2018</t>
+          <t>Xavier Frissant Touraine Amboise L'Orée des Frênes 2015</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -6654,19 +6654,19 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ollieux Romanis Corbières Classique 2018</t>
+          <t>Parés Baltà Penedès Indigena 2017</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D297" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E297" t="n">
         <v>36</v>
@@ -6675,19 +6675,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Parés Baltà Penedès Indigena 2017</t>
+          <t>Ollieux Romanis Corbières Classique 2018</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D298" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E298" t="n">
         <v>36</v>
@@ -6759,19 +6759,19 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Xavier Frissant Touraine Amboise M de La Touche 2016</t>
+          <t>Camille Giroud Maranges Rouge 1er Cru Le Croix Moines 2016</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>8.9</v>
+        <v>35.6</v>
       </c>
       <c r="D302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E302" t="n">
         <v>35.6</v>
@@ -6780,19 +6780,19 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Camille Giroud Maranges Rouge 1er Cru Le Croix Moines 2016</t>
+          <t>Xavier Frissant Touraine Amboise M de La Touche 2016</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>35.6</v>
+        <v>8.9</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E303" t="n">
         <v>35.6</v>
@@ -6990,19 +6990,19 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Château Ollieux Romanis Corbières Rosé Classique 2019</t>
+          <t>Domaine de Montgilet Anjou Rouge Les Yvonnais 2015</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>8.199999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="D313" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E313" t="n">
         <v>32.8</v>
@@ -7011,19 +7011,19 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Domaine de Montgilet Anjou Rouge Les Yvonnais 2015</t>
+          <t>Château Ollieux Romanis Corbières Rosé Classique 2019</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>16.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D314" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E314" t="n">
         <v>32.8</v>
@@ -7200,19 +7200,19 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Vincent Carême Vouvray Sec 2018</t>
+          <t>Domaine Bulliat Beaujolais Villages Bibine 2018</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E323" t="n">
         <v>28.8</v>
@@ -7221,19 +7221,19 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Domaine Bulliat Beaujolais Villages Bibine 2018</t>
+          <t>Vincent Carême Vouvray Sec 2018</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E324" t="n">
         <v>28.8</v>
@@ -7956,12 +7956,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>David-Beaupère Juliénas Les Trois Verres 2018</t>
+          <t>Domaine Bulliat Morgon Le Colombier 2019</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -7977,12 +7977,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Domaine Bulliat Morgon Le Colombier 2019</t>
+          <t>David-Beaupère Juliénas Les Trois Verres 2018</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -8061,12 +8061,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Maurice Schoech Crémant d'Alsace Brut Rosé Bulles de Granite</t>
+          <t>François Baur Pinot Gris Herrenweg de Turckheim 2018</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -8082,12 +8082,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>François Baur Pinot Gris Herrenweg de Turckheim 2018</t>
+          <t>Maurice Schoech Crémant d'Alsace Brut Rosé Bulles de Granite</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -8229,12 +8229,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Triennes IGP Méditerranée Rouge Merlot 2016</t>
+          <t>Domaine de l'Idylle Roussette de Savoie Anne de Chypre 2018</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -8250,12 +8250,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Domaine de l'Idylle Roussette de Savoie Anne de Chypre 2018</t>
+          <t>Triennes IGP Méditerranée Rouge Merlot 2016</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -8439,12 +8439,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Parcé Frères IGP Pays d'Oc Zoé Viognier 2019</t>
+          <t>Parcé Frères IGP Côtes Catalanes Hommage à Fernand Blanc 2019</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -8460,12 +8460,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Parcé Frères IGP Côtes Catalanes Hommage à Fernand Blanc 2019</t>
+          <t>Parcé Frères IGP Pays d'Oc Zoé Viognier 2019</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -8544,16 +8544,16 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Riesling Grand Cru Rangen De Thann Clos Saint-Urbain 2017</t>
+          <t>Plateau des Chênes Lirac 2015</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="D387" t="n">
         <v>0</v>
@@ -8565,16 +8565,16 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Catherine et Claude Maréchal Savigny-Lès-Beaune Rouge 2017</t>
+          <t>Saumaize-Michelin Mâcon Vergisson Sur La Roche 2017</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>35.6</v>
+        <v>18.7</v>
       </c>
       <c r="D388" t="n">
         <v>0</v>
@@ -8586,16 +8586,16 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Sancerre Rouge La Demoiselle 2015</t>
+          <t>Paul Ginglinger Pinot Gris Grand Cru Eichberg 2015</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>57</v>
+        <v>22.8</v>
       </c>
       <c r="D389" t="n">
         <v>0</v>
@@ -8607,16 +8607,16 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Parés Baltà Penedès Hisenda Miret 2013</t>
+          <t>Emile Boeckel Gewurztraminer Grand Cru Zotzenberg 2016</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>25</v>
+        <v>15.8</v>
       </c>
       <c r="D390" t="n">
         <v>0</v>
@@ -8628,16 +8628,16 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lucien Boillot Gevrey Chambertin Les Evocelles 2017</t>
+          <t>Jean-Batiste Arena Muscat du Cap Corse 2015</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>52.6</v>
+        <v>28</v>
       </c>
       <c r="D391" t="n">
         <v>0</v>
@@ -8649,16 +8649,16 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Champagne Agrapart &amp;amp; Fils Les 7 Crus Brut Blanc de Blancs</t>
+          <t>Château La Tour l'Aspic Pauillac 2014</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>45</v>
+        <v>26.5</v>
       </c>
       <c r="D392" t="n">
         <v>0</v>
@@ -8670,16 +8670,16 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois D.D. 2016</t>
+          <t>Domaine Peyre Rose Syrah Léone 2008</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>18.25</v>
+        <v>78</v>
       </c>
       <c r="D393" t="n">
         <v>0</v>
@@ -8691,16 +8691,16 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Argentine Mendoza Alamos Torrontes 2017</t>
+          <t>Domaine des Comtes Lafon Monthélie 1er Cru Les Duresses 2017</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>11.1</v>
+        <v>55.6</v>
       </c>
       <c r="D394" t="n">
         <v>0</v>
@@ -8712,16 +8712,16 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Château Carbonnieux Graves Blanc 2017</t>
+          <t>Champagne Agrapart &amp;amp; Fils Les 7 Crus Brut Blanc de Blancs</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>40.2</v>
+        <v>45</v>
       </c>
       <c r="D395" t="n">
         <v>0</v>
@@ -8733,16 +8733,16 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Camin Larredya Jurançon Moelleux Au Capcéu 2018</t>
+          <t>Zind-Humbrecht Riesling Grand Cru Rangen De Thann Clos Saint-Urbain 2017</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D396" t="n">
         <v>0</v>
@@ -8754,16 +8754,16 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Domaine de Montgilet Coteaux de l'Aubance Les Trois Schistes 2016</t>
+          <t>Chili Valdivieso Merlot 2017</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>27.9</v>
+        <v>10.7</v>
       </c>
       <c r="D397" t="n">
         <v>0</v>
@@ -8775,16 +8775,16 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Camille Giroud Clos de Vougeot 2016</t>
+          <t>Parcé Frères Côtes du Roussillon Villages Hommage à Fernand 2017</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>175</v>
+        <v>7.2</v>
       </c>
       <c r="D398" t="n">
         <v>0</v>
@@ -8796,16 +8796,16 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Domaine des Terres d'Ocre Saint-Pourçain Blanc Instant T 2018</t>
+          <t>Domaine Huet Vouvray Le Clos du Bourg Moelleux Première Trie 2008</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>10.3</v>
+        <v>59.6</v>
       </c>
       <c r="D399" t="n">
         <v>0</v>
@@ -8817,16 +8817,16 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois Vin Jaune En Spois 2011</t>
+          <t>Domaine Bulliat Moulin-à-Vent 2017</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>62.4</v>
+        <v>11.5</v>
       </c>
       <c r="D400" t="n">
         <v>0</v>
@@ -8838,16 +8838,16 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Domaine Peyre Rose Syrah Léone 2008</t>
+          <t>Marc Colin Et Fils Chassagne-Montrachet Blanc Les Vide-Bourses 1er Cru 2016</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>78</v>
+        <v>61.6</v>
       </c>
       <c r="D401" t="n">
         <v>0</v>
@@ -8859,16 +8859,16 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Darnley's London Dry Gin Original</t>
+          <t>Tempier Bandol Migoua 2017</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D402" t="n">
         <v>0</v>
@@ -8880,16 +8880,16 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Maison Trimbach Riesling Grand Cru Geisberg 2012</t>
+          <t>Lucien Boillot Puligny-Montrachet 1er Cru Les Perrières 2016</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>57.6</v>
+        <v>83.7</v>
       </c>
       <c r="D403" t="n">
         <v>0</v>
@@ -8901,16 +8901,16 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Christophe Pichon Condrieu 2017</t>
+          <t>Domaine Clerget Vosne-Romanée Les Violettes 2015</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>38.5</v>
+        <v>57</v>
       </c>
       <c r="D404" t="n">
         <v>0</v>
@@ -8922,16 +8922,16 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Gilles Robin Cornas 2016</t>
+          <t>François Bergeret Hautes Côtes de Beaune Vieilles Vignes Rondo 2017</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>46</v>
+        <v>13.4</v>
       </c>
       <c r="D405" t="n">
         <v>0</v>
@@ -8943,16 +8943,16 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Chili De Martino Gallardia Cinsault 2017</t>
+          <t>Château Tour De Pez Saint-Estèphe Les Hauts de Pez 2016</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="D406" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Weingut Besson-Strasser Zürich Blauer Zweigelt 2016</t>
+          <t>Marcel Windholtz Eau de Vie de Baie de Houx</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>32.2</v>
+        <v>76.8</v>
       </c>
       <c r="D407" t="n">
         <v>0</v>
@@ -8985,16 +8985,16 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Albert Boxler Riesling Grand Cru Sommerberg "E" 2018</t>
+          <t>Domaine de Montbourgeau L'Etoile En Banode 2016</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>71.3</v>
+        <v>19.8</v>
       </c>
       <c r="D408" t="n">
         <v>0</v>
@@ -9006,16 +9006,16 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Le Mont Moelleux 2015</t>
+          <t>Marcel Windholtz Eau de Vie de Marc de Gewurztraminer</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>31.7</v>
+        <v>41</v>
       </c>
       <c r="D409" t="n">
         <v>0</v>
@@ -9027,16 +9027,16 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Emile Boeckel Gewurztraminer Grand Cru Zotzenberg 2016</t>
+          <t>I Fabbri Chianti Classico Gran Selezione 2015</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>15.8</v>
+        <v>48.5</v>
       </c>
       <c r="D410" t="n">
         <v>0</v>
@@ -9048,16 +9048,16 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nouvelle-Zélande Marlborough Momo Pinot Noir 2016</t>
+          <t>Domaine Rotier Gaillac Blanc Doux Les Gravels 2016</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>22.8</v>
+        <v>12.9</v>
       </c>
       <c r="D411" t="n">
         <v>0</v>
@@ -9069,16 +9069,16 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Albert Mann Pinot Noir Grand P 2017</t>
+          <t>Domaine Rotier Gaillac Rouge L'Ame 2016</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>59.9</v>
+        <v>29.8</v>
       </c>
       <c r="D412" t="n">
         <v>0</v>
@@ -9090,16 +9090,16 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Saumaize-Michelin Pouilly-Fuissé Vignes Blanches 2018</t>
+          <t>David Duband Charmes-Chambertin Grand Cru 2014</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>25.3</v>
+        <v>217.5</v>
       </c>
       <c r="D413" t="n">
         <v>0</v>
@@ -9111,16 +9111,16 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Vincent Carême Vouvray Moelleux 2015</t>
+          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2018</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>21</v>
+        <v>32.8</v>
       </c>
       <c r="D414" t="n">
         <v>0</v>
@@ -9132,16 +9132,16 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>La Cotelleraie Saint-Nicolas-de-Bourgueil Le Vau Jaumier 2016</t>
+          <t>Gratavinum Priorat 2?r 2017</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>16.4</v>
+        <v>21.8</v>
       </c>
       <c r="D415" t="n">
         <v>0</v>
@@ -9153,16 +9153,16 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Camille Giroud Marsannay Rouge Les Longeroies 2016</t>
+          <t>Domaine Saint-Nicolas Vin de France Blanc Les Clous 2019</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>33.6</v>
+        <v>16.3</v>
       </c>
       <c r="D416" t="n">
         <v>0</v>
@@ -9174,16 +9174,16 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Domaine Des Croix Corton Grand Cru Les Grèves 2017</t>
+          <t>Le Vieux Donjon Châteauneuf-du-Pape 2013</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>102.3</v>
+        <v>37</v>
       </c>
       <c r="D417" t="n">
         <v>0</v>
@@ -9195,16 +9195,16 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Camille Giroud Auxey-Duresses Blanc 2017</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2013</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>35.6</v>
+        <v>105</v>
       </c>
       <c r="D418" t="n">
         <v>0</v>
@@ -9216,16 +9216,16 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Maurice Schoech Pinot Noir Pièce de Chêne 2016</t>
+          <t>Parés Baltà Cava Brut Nature</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="D419" t="n">
         <v>0</v>
@@ -9237,16 +9237,16 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Domaine Hauvette IGP Alpilles Dolia 2012</t>
+          <t>Domaine Augustin Collioure Blanc Adéodat 2019</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>44.6</v>
+        <v>28</v>
       </c>
       <c r="D420" t="n">
         <v>0</v>
@@ -9258,16 +9258,16 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Gratavinum Priorat 2?r 2017</t>
+          <t>Domaine Huet Vouvray Haut-Lieu Sec 2017</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>21.8</v>
+        <v>24.4</v>
       </c>
       <c r="D421" t="n">
         <v>0</v>
@@ -9279,16 +9279,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Château Saransot-Dupré Listrac-Médoc 2016</t>
+          <t>Domaine Sérol Côte Roannaise Les Originelles 2019</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>17.2</v>
+        <v>10.2</v>
       </c>
       <c r="D422" t="n">
         <v>0</v>
@@ -9300,16 +9300,16 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>I Fabbri Chianti Classico Gran Selezione 2015</t>
+          <t>Maison Trimbach Riesling Grand Cru Schlossberg 2015</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>48.5</v>
+        <v>63.5</v>
       </c>
       <c r="D423" t="n">
         <v>0</v>
@@ -9321,16 +9321,16 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Les Mémoires 2018</t>
+          <t>La Préceptorie Côtes du Roussillon Blanc Coume Marie 2018</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>42.2</v>
+        <v>13.5</v>
       </c>
       <c r="D424" t="n">
         <v>0</v>
@@ -9342,16 +9342,16 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Château Simone Palette Blanc 2017</t>
+          <t>Domaine de Montcalmès Coteaux du Languedoc Blanc 2017</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>46.5</v>
+        <v>28.5</v>
       </c>
       <c r="D425" t="n">
         <v>0</v>
@@ -9363,16 +9363,16 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur Blanc Clos Roman 2016</t>
+          <t>Marc Colin Et Fils Chassagne-Montrachet Rouge Vieilles Vignes 2017</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>57.7</v>
+        <v>26.5</v>
       </c>
       <c r="D426" t="n">
         <v>0</v>
@@ -9384,16 +9384,16 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Champagne Egly-Ouriet Grand Cru Extra Brut V.P.</t>
+          <t>Thierry Germain Saumur-Champigny Les Mémoires 2018</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>79.5</v>
+        <v>42.2</v>
       </c>
       <c r="D427" t="n">
         <v>0</v>
@@ -9405,16 +9405,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Alastro 2017</t>
+          <t>Thierry Germain Saumur-Champigny Outre Terre 2014</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D428" t="n">
         <v>0</v>
@@ -9426,16 +9426,16 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Maurice Schoech Gewurztraminer 2018</t>
+          <t>Weingut Besson-Strasser Zürich Pinot Noir Albi 2016</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>12.1</v>
+        <v>47.2</v>
       </c>
       <c r="D429" t="n">
         <v>0</v>
@@ -9447,16 +9447,16 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Domaine Augustin Collioure Blanc Adéodat 2019</t>
+          <t>Domaine Hauvette IGP Alpilles Dolia 2013</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>28</v>
+        <v>48.5</v>
       </c>
       <c r="D430" t="n">
         <v>0</v>
@@ -9468,16 +9468,16 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Château de Vaudieu Châteauneuf-du-Pape Amiral G 2015</t>
+          <t>Rimauresq Côtes de Provence Blanc Cru Classé "R" 2019</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>71.7</v>
+        <v>17</v>
       </c>
       <c r="D431" t="n">
         <v>0</v>
@@ -9489,16 +9489,16 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge Cuvée Jacques 2016</t>
+          <t>Zind-Humbrecht Pinot Gris Roche Calcaire 2017</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>24.3</v>
+        <v>23</v>
       </c>
       <c r="D432" t="n">
         <v>0</v>
@@ -9510,16 +9510,16 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Mérieau Touraine L'Arpent des Vaudons 2018</t>
+          <t>Zind-Humbrecht Muscat Grand Cru Goldert 2015</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>9.6</v>
+        <v>29.8</v>
       </c>
       <c r="D433" t="n">
         <v>0</v>
@@ -9531,16 +9531,16 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Champagne Mailly Grand Cru Brut Réserve</t>
+          <t>Chili Errazuriz Cabernet Sauvignon 2016</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>29.5</v>
+        <v>12.7</v>
       </c>
       <c r="D434" t="n">
         <v>0</v>
@@ -9552,16 +9552,16 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Saumaize-Michelin Pouilly-Fuissé Les Ronchevats 2018</t>
+          <t>La Préceptorie Maury Blanc 2015</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>27.9</v>
+        <v>16.3</v>
       </c>
       <c r="D435" t="n">
         <v>0</v>
@@ -9573,16 +9573,16 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Château de Cazeneuve Languedoc Blanc 2016</t>
+          <t>Parcé Frères Banyuls Rimage 2018</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>18.9</v>
+        <v>16.2</v>
       </c>
       <c r="D436" t="n">
         <v>0</v>
@@ -9594,16 +9594,16 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Clos de l'Echelier 2017</t>
+          <t>Domaine Huet Vouvray Le Mont Moelleux 2015</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>38</v>
+        <v>31.7</v>
       </c>
       <c r="D437" t="n">
         <v>0</v>
@@ -9615,16 +9615,16 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Treacle Chest</t>
+          <t>Tempier Bandol Cabassaou 2017</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>59.8</v>
+        <v>92</v>
       </c>
       <c r="D438" t="n">
         <v>0</v>
@@ -9636,16 +9636,16 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Champagne Egly-Ouriet Grand Cru Brut Tradition</t>
+          <t>Domaine de l'Idylle Savoie Cruet 2018</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>59</v>
+        <v>8.1</v>
       </c>
       <c r="D439" t="n">
         <v>0</v>
@@ -9657,16 +9657,16 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Domaine Rotier Gaillac Rouge L'Ame 2016</t>
+          <t>Parés Baltà Penedès Hisenda Miret 2013</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>29.8</v>
+        <v>25</v>
       </c>
       <c r="D440" t="n">
         <v>0</v>
@@ -9678,16 +9678,16 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Catherine et Claude Maréchal Pommard La Chanière 2017</t>
+          <t>Champagne Egly-Ouriet Grand Cru Extra Brut V.P.</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>50.4</v>
+        <v>79.5</v>
       </c>
       <c r="D441" t="n">
         <v>0</v>
@@ -9699,16 +9699,16 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Monthélie 1er Cru Les Duresses 2017</t>
+          <t>Champagne Larmandier-Bernier Latitude</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>55.6</v>
+        <v>39</v>
       </c>
       <c r="D442" t="n">
         <v>0</v>
@@ -9720,16 +9720,16 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky The Hive 12 ans</t>
+          <t>Château Tour De Pez Saint-Estèphe 2017</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D443" t="n">
         <v>0</v>
@@ -9741,16 +9741,16 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Cognac Frapin 1270</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Spice King</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>44</v>
+        <v>49.5</v>
       </c>
       <c r="D444" t="n">
         <v>0</v>
@@ -9762,16 +9762,16 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Saumaize-Michelin Saint-Véran Les Crèches 2018</t>
+          <t>Château de Vaudieu Châteauneuf-du-Pape Amiral G 2015</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>19.3</v>
+        <v>71.7</v>
       </c>
       <c r="D445" t="n">
         <v>0</v>
@@ -9783,16 +9783,16 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Franc De Pied 2016</t>
+          <t>Christophe Pichon Condrieu 2017</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>36.2</v>
+        <v>38.5</v>
       </c>
       <c r="D446" t="n">
         <v>0</v>
@@ -9804,16 +9804,16 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Cognac Frapin Château de Fontpinot 1989 20 Ans d'Age</t>
+          <t>Stéphane Tissot Arbois Trousseau Amphore 2017</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>157</v>
+        <v>40.7</v>
       </c>
       <c r="D447" t="n">
         <v>0</v>
@@ -9846,16 +9846,16 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>La Préceptorie Maury Blanc 2015</t>
+          <t>Stéphane Tissot Arbois Vin Jaune En Spois 2011</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>16.3</v>
+        <v>62.4</v>
       </c>
       <c r="D449" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Domaine Peyre Rose Oro Blanc 2002</t>
+          <t>Moulin de Gassac IGP Pays d'Hérault Rouge Mazet du Levant 2017</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>78</v>
+        <v>10.6</v>
       </c>
       <c r="D450" t="n">
         <v>0</v>
@@ -9888,16 +9888,16 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Marcel Richaud Cairanne Rouge L'Ebrescade 2017</t>
+          <t>Marcel Windholtz Eau de Vie de Quetsch d'Alsace Réserve Particulière</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>27.8</v>
+        <v>50</v>
       </c>
       <c r="D451" t="n">
         <v>0</v>
@@ -9909,16 +9909,16 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Château Dutruch Grand Poujeaux Moulis 2016</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2016</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>18.5</v>
+        <v>121</v>
       </c>
       <c r="D452" t="n">
         <v>0</v>
@@ -9930,16 +9930,16 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Parcé Frères Côtes du Roussillon Villages Hommage à Fernand 2017</t>
+          <t>Domaine de Montgilet Coteaux de l'Aubance Les Trois Schistes 2016</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>7.2</v>
+        <v>27.9</v>
       </c>
       <c r="D453" t="n">
         <v>0</v>
@@ -9951,16 +9951,16 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Domaine de la Monardière Vacqueyras Blanc Galéjade 2018</t>
+          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge Reflets 2018</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>24.4</v>
+        <v>16.9</v>
       </c>
       <c r="D454" t="n">
         <v>0</v>
@@ -9972,16 +9972,16 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Château de Villeneuve Saumur-Champigny Le Grand Clos 2017</t>
+          <t>Maurice Schoech Pinot Noir Pièce de Chêne 2016</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>29.8</v>
+        <v>13.6</v>
       </c>
       <c r="D455" t="n">
         <v>0</v>
@@ -9993,16 +9993,16 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Saumaize-Michelin Mâcon Vergisson Sur La Roche 2017</t>
+          <t>Marcel Richaud Cairanne Rouge L'Ebrescade 2017</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>18.7</v>
+        <v>27.8</v>
       </c>
       <c r="D456" t="n">
         <v>0</v>
@@ -10014,16 +10014,16 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Jacqueson Rully Rouge 1er Cru Les Preaux 2018</t>
+          <t>Thierry Germain Saumur-Champigny Outre Terre 2017</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>24.5</v>
+        <v>48.8</v>
       </c>
       <c r="D457" t="n">
         <v>0</v>
@@ -10035,16 +10035,16 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Parcé Frères Banyuls Rimage 2018</t>
+          <t>Tempier Bandol Tourtine 2017</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>16.2</v>
+        <v>58</v>
       </c>
       <c r="D458" t="n">
         <v>0</v>
@@ -10056,16 +10056,16 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Champagne Larmandier-Bernier Terre de Vertus Premier Cru 2011</t>
+          <t>Planeta Sicilia Alastro 2017</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>49.5</v>
+        <v>12</v>
       </c>
       <c r="D459" t="n">
         <v>0</v>
@@ -10077,16 +10077,16 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Decelle-Villa Côte de Nuits Villages "Aux Montagnes" 2014</t>
+          <t>Albert Boxler Riesling Grand Cru Sommerberg "D" 2018</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>28.4</v>
+        <v>71.3</v>
       </c>
       <c r="D460" t="n">
         <v>0</v>
@@ -10098,16 +10098,16 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Decelle-Villa Saint-Aubin 1er Cru Sous Roche Dumay 2015</t>
+          <t>Planeta Sicilia Etna Bianco 2018</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>44</v>
+        <v>17.5</v>
       </c>
       <c r="D461" t="n">
         <v>0</v>
@@ -10119,16 +10119,16 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Paul Ginglinger Pinot Gris Grand Cru Eichberg 2015</t>
+          <t>Camille Giroud Auxey-Duresses Blanc 2017</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>22.8</v>
+        <v>35.6</v>
       </c>
       <c r="D462" t="n">
         <v>0</v>
@@ -10140,16 +10140,16 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Domaine de l'Idylle Savoie Cruet 2018</t>
+          <t>Château Saransot-Dupré Bordeaux Blanc 2016</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>8.1</v>
+        <v>12.5</v>
       </c>
       <c r="D463" t="n">
         <v>0</v>
@@ -10161,16 +10161,16 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Domaine Rotier Gaillac Blanc Sec Renaissance 2015</t>
+          <t>Domaine Huet Vouvray Haut-Lieu Demi-Sec 2015</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>10.7</v>
+        <v>26.9</v>
       </c>
       <c r="D464" t="n">
         <v>0</v>
@@ -10182,16 +10182,16 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Domaine de Montbourgeau L'Etoile En Banode 2016</t>
+          <t>Wemyss Malts Single Cask Scotch Whisky Chocolate Moka Cake 2005 Strathclyde</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>19.8</v>
+        <v>93</v>
       </c>
       <c r="D465" t="n">
         <v>0</v>
@@ -10203,16 +10203,16 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Domaine de Vaccelli AOP Ajaccio Rouge Granit 174 2017</t>
+          <t>Wemyss Malts Single Cask Scotch Whisky Chai Caramel Latte 2002 Craigellachie</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>74.5</v>
+        <v>114</v>
       </c>
       <c r="D466" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Château-Chalon 2011</t>
+          <t>Domaine Labranche Laffont Madiran Tradition 2016</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>74.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D467" t="n">
         <v>0</v>
@@ -10245,16 +10245,16 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Prunelle Sauvage</t>
+          <t>Pierre Martin Sancerre Les Monts Damnés 2018</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>52.9</v>
+        <v>20.8</v>
       </c>
       <c r="D468" t="n">
         <v>0</v>
@@ -10266,16 +10266,16 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Pinot Gris Roche Calcaire 2017</t>
+          <t>La Cotelleraie Saint-Nicolas-de-Bourgueil Le Vau Jaumier 2016</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>23</v>
+        <v>16.4</v>
       </c>
       <c r="D469" t="n">
         <v>0</v>
@@ -10287,16 +10287,16 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Franc De Pied 2017</t>
+          <t>Stéphane Tissot Arbois Blanc La Mailloche 2016</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="D470" t="n">
         <v>0</v>
@@ -10308,16 +10308,16 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Domaine Des Croix Beaune 1er Cru Les Cent Vignes 2017</t>
+          <t>Maurice Schoech Gewurztraminer 2018</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>41</v>
+        <v>12.1</v>
       </c>
       <c r="D471" t="n">
         <v>0</v>
@@ -10329,16 +10329,16 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Domaine Labranche Laffont Pacherenc du Vic-Bilh Sec 2017</t>
+          <t>Stéphane Tissot Château-Chalon 2011</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>12.7</v>
+        <v>74.8</v>
       </c>
       <c r="D472" t="n">
         <v>0</v>
@@ -10350,16 +10350,16 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Catherine et Claude Maréchal Savigny-Lès-Beaune Rouge 2016</t>
+          <t>Domaine Peyre Rose Oro Blanc 2002</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>32.2</v>
+        <v>78</v>
       </c>
       <c r="D473" t="n">
         <v>0</v>
@@ -10371,16 +10371,16 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Muscat Grand Cru Goldert 2015</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2014</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>29.8</v>
+        <v>115</v>
       </c>
       <c r="D474" t="n">
         <v>0</v>
@@ -10392,16 +10392,16 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Château de Villeneuve Saumur-Champigny Clos de la Bienboire 2018</t>
+          <t>Nouvelle-Zélande Marlborough Momo Pinot Noir 2016</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>13.4</v>
+        <v>22.8</v>
       </c>
       <c r="D475" t="n">
         <v>0</v>
@@ -10413,16 +10413,16 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Domaine Pellé Menetou Salon Rouge Les Cris 2015</t>
+          <t>Château de la Selve Coteaux de l'Ardèche Rouge Serre de Berty 2014</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>21.9</v>
+        <v>18.2</v>
       </c>
       <c r="D476" t="n">
         <v>0</v>
@@ -10434,16 +10434,16 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Pierre Martin Sancerre Les Monts Damnés 2018</t>
+          <t>Albert Boxler Riesling Grand Cru Sommerberg "E" 2018</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>20.8</v>
+        <v>71.3</v>
       </c>
       <c r="D477" t="n">
         <v>0</v>
@@ -10455,16 +10455,16 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Wemyss Malts Single Cask Scotch Whisky Choc 'n' Nut Pretzel 2001 Bunnahabhain</t>
+          <t>Marc Colin Et Fils Saint-Aubin 1er Cru La Chatenière 2017</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>122</v>
+        <v>41.8</v>
       </c>
       <c r="D478" t="n">
         <v>0</v>
@@ -10476,16 +10476,16 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Domaine Jamet Côte Rôtie Fructus Voluptas 2018</t>
+          <t>La Préceptorie Côtes du Roussillon Blanc Terres Nouvelles 2018</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="D479" t="n">
         <v>0</v>
@@ -10497,16 +10497,16 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois Blanc La Mailloche 2016</t>
+          <t>Pierre Gaillard Côtes-du-Rhône Blanc Les Gendrines 2018</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>36.9</v>
+        <v>18.3</v>
       </c>
       <c r="D480" t="n">
         <v>0</v>
@@ -10518,16 +10518,16 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Domaine Saint-Nicolas Vin de France Blanc Les Clous 2019</t>
+          <t>François Baur Gewurztraminer Herrenweg de Turckheim 2016</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="D481" t="n">
         <v>0</v>
@@ -10539,16 +10539,16 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Paul Ginglinger Riesling Drei Exa 2018</t>
+          <t>Champagne Mailly Grand Cru Brut Réserve</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>12.8</v>
+        <v>29.5</v>
       </c>
       <c r="D482" t="n">
         <v>0</v>
@@ -10560,16 +10560,16 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Domaine de Bellivière Jasnières Les Rosiers 2015</t>
+          <t>Huiles d'Olive Extra Vierge Planeta 3x 10cl</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>29.9</v>
+        <v>19.5</v>
       </c>
       <c r="D483" t="n">
         <v>0</v>
@@ -10581,16 +10581,16 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Domaine Labranche Laffont Madiran Vieilles Vignes 2015</t>
+          <t>Champagne Mailly Grand Cru Intemporelle Rosé 2009</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>15.4</v>
+        <v>69</v>
       </c>
       <c r="D484" t="n">
         <v>0</v>
@@ -10602,16 +10602,16 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Champagne Agrapart &amp;amp; Fils L'Avizoise Extra Brut Blanc de Blancs Grand Cru 2012</t>
+          <t>Le Pas de l'Escalette Terrasses du Larzac Le Pas de D. 2017</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>112</v>
+        <v>20.4</v>
       </c>
       <c r="D485" t="n">
         <v>0</v>
@@ -10623,16 +10623,16 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Domaine Schoenheitz Pinot Noir Val Saint Grégoire 2017</t>
+          <t>Tempier Bandol Blanc 2018</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>18.2</v>
+        <v>27.9</v>
       </c>
       <c r="D486" t="n">
         <v>0</v>
@@ -10644,16 +10644,16 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Domaine Clerget Echezeaux Grand Cru En Orveaux 2015</t>
+          <t>Domaine de l'Hortus Val de Montferrand La Grande Cuvée Blanc 2018</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>116.4</v>
+        <v>24</v>
       </c>
       <c r="D487" t="n">
         <v>0</v>
@@ -10665,16 +10665,16 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Domaine Peyre Rose Marlène N°3 2008</t>
+          <t>Château Jean Faure Saint-Emilion Grand Cru 2015</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>78</v>
+        <v>50.5</v>
       </c>
       <c r="D488" t="n">
         <v>0</v>
@@ -10686,16 +10686,16 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Château de Cazeneuve Val de Montferrand Rouge Caza Sorix 2019</t>
+          <t>Champagne Mailly Grand Cru Les Echansons 2007</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>11.6</v>
+        <v>83</v>
       </c>
       <c r="D489" t="n">
         <v>0</v>
@@ -10707,16 +10707,16 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Wemyss Malts Single Cask Scotch Whisky Chocolate Moka Cake 2005 Strathclyde</t>
+          <t>Pierre Jean Villa Côte Rôtie Carmina 2017</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="D490" t="n">
         <v>0</v>
@@ -10728,16 +10728,16 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Noto Santa Cecilia 2016</t>
+          <t>Champagne Egly-Ouriet Grand Cru Brut Tradition</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>29.9</v>
+        <v>59</v>
       </c>
       <c r="D491" t="n">
         <v>0</v>
@@ -10749,16 +10749,16 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Domaine de La Tour Du Bon Bandol Rouge Saint Ferréol 2005</t>
+          <t>Alphonse Mellot Sancerre Rouge La Demoiselle 2015</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D492" t="n">
         <v>0</v>
@@ -10791,16 +10791,16 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Eruzione 1614 2017</t>
+          <t>Champagne Mailly Grand Cru Brut Rosé</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>23.5</v>
+        <v>37.5</v>
       </c>
       <c r="D494" t="n">
         <v>0</v>
@@ -10812,16 +10812,16 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Tempier Bandol Cabassaou 2017</t>
+          <t>Domaine Rotier Gaillac Rouge Renaissance 2016</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>92</v>
+        <v>13.2</v>
       </c>
       <c r="D495" t="n">
         <v>0</v>
@@ -10833,16 +10833,16 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2014</t>
+          <t>Mas de Daumas Gassac IGP Saint-Guilhem-le-Désert 2018</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="D496" t="n">
         <v>0</v>
@@ -10854,16 +10854,16 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Le Pas de l'Escalette Terrasses du Larzac Le Grand Pas 2018</t>
+          <t>Château Dutruch Grand Poujeaux Moulis 2016</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>27.5</v>
+        <v>18.5</v>
       </c>
       <c r="D497" t="n">
         <v>0</v>
@@ -10875,16 +10875,16 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Marc Colin Et Fils Santenay Rouge 2017</t>
+          <t>Liban Vallée de la Békaa Château Marsyas 2012</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>26.5</v>
+        <v>28.8</v>
       </c>
       <c r="D498" t="n">
         <v>0</v>
@@ -10896,16 +10896,16 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Marc de Gewurztraminer</t>
+          <t>Marc Colin Et Fils Santenay Rouge 2017</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>41</v>
+        <v>26.5</v>
       </c>
       <c r="D499" t="n">
         <v>0</v>
@@ -10917,16 +10917,16 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Marcel Richaud Cairanne Rouge 2018</t>
+          <t>Thierry Germain Saumur-Champigny Franc De Pied 2017</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>18.4</v>
+        <v>36.3</v>
       </c>
       <c r="D500" t="n">
         <v>0</v>
@@ -10938,16 +10938,16 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Philippe Alliet Chinon Rouge Coteau de Noiré 2016</t>
+          <t>Château de Cazeneuve Val de Montferrand Rouge Caza Sorix 2019</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>31.7</v>
+        <v>11.6</v>
       </c>
       <c r="D501" t="n">
         <v>0</v>
@@ -10959,16 +10959,16 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Pierre Jean Villa Saint-Joseph Saut De l'Ange 2018</t>
+          <t>Domaine Huet Vouvray Le Clos du Bourg Demi-Sec 2017</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>34.3</v>
+        <v>34.7</v>
       </c>
       <c r="D502" t="n">
         <v>0</v>
@@ -10980,16 +10980,16 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Outre Terre 2014</t>
+          <t>Wemyss Malts Blended Scotch Whisky Lord Elcho</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>43</v>
+        <v>27.5</v>
       </c>
       <c r="D503" t="n">
         <v>0</v>
@@ -11001,16 +11001,16 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Thevenet Quintaine Viré-Clessé La Bongran 2015</t>
+          <t>Domaine Clerget Chambolle-Musigny 2014</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>24.7</v>
+        <v>42.1</v>
       </c>
       <c r="D504" t="n">
         <v>0</v>
@@ -11022,16 +11022,16 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Château Saransot-Dupré Bordeaux Blanc 2016</t>
+          <t>Thierry Germain Saumur-Champigny Outre Terre 2013</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>12.5</v>
+        <v>43</v>
       </c>
       <c r="D505" t="n">
         <v>0</v>
@@ -11043,16 +11043,16 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Le Pas de l'Escalette Terrasses du Larzac Le Pas de D. 2017</t>
+          <t>Domaine Pellé Sancerre Rouge La Croix Au Garde 2017</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="D506" t="n">
         <v>0</v>
@@ -11064,16 +11064,16 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Domaine Peyre Rose Clos des Cistes 2008</t>
+          <t>Kingsbarns Distillery Lowland Single Malt Whisky</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D507" t="n">
         <v>0</v>
@@ -11085,16 +11085,16 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Spice King</t>
+          <t>Zind-Humbrecht Gewurztraminer Clos Windsbuhl 2012</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>49.5</v>
+        <v>56.3</v>
       </c>
       <c r="D508" t="n">
         <v>0</v>
@@ -11106,16 +11106,16 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Marc Colin Et Fils Saint-Aubin 1er Cru La Chatenière 2017</t>
+          <t>Domaine Schoenheitz Pinot Blanc Val Saint Grégoire 2017</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>41.8</v>
+        <v>11.1</v>
       </c>
       <c r="D509" t="n">
         <v>0</v>
@@ -11127,16 +11127,16 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Albert Boxler Pinot Gris Grand Cru Sommerberg "W" 2016</t>
+          <t>Zind-Humbrecht Riesling Clos Windsbuhl 2014</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>56.4</v>
+        <v>69</v>
       </c>
       <c r="D510" t="n">
         <v>0</v>
@@ -11148,16 +11148,16 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Domaine Plageoles Vin de France Contre-Pied 2016</t>
+          <t>Jacqueson Rully Rouge 1er Cru Les Preaux 2018</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>12.8</v>
+        <v>24.5</v>
       </c>
       <c r="D511" t="n">
         <v>0</v>
@@ -11169,16 +11169,16 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Domaine de La Tour Du Bon Bandol Rouge Saint Ferréol 2018</t>
+          <t>Borie La Vitarèle Saint-Chinian Midi Rouge 2015</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>39.1</v>
+        <v>40.5</v>
       </c>
       <c r="D512" t="n">
         <v>0</v>
@@ -11190,16 +11190,16 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Domaine Des Croix Savigny-Lès-Beaune 1er Cru Les Peuillets 2015</t>
+          <t>Clos du Mont-Olivet Vins de Pays du Gard Confluence 2017</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>46</v>
+        <v>13.5</v>
       </c>
       <c r="D513" t="n">
         <v>0</v>
@@ -11211,16 +11211,16 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Pinot Gris Grand Cru Rangen De Thann Clos Saint-Urbain 2012</t>
+          <t>Domaine La Croix Belle Côtes de Thongue Blanc Champ des Lys 2018</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>88.40000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="D514" t="n">
         <v>0</v>
@@ -11232,16 +11232,16 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Château Peymartin Saint-Julien 2014</t>
+          <t>Domaine Rouge Garance Côtes du Rhône Villages Garances 2016</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>23.8</v>
+        <v>12.5</v>
       </c>
       <c r="D515" t="n">
         <v>0</v>
@@ -11253,16 +11253,16 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Etna Rosso 2018</t>
+          <t>Domaine des Bosquets Gigondas 2016</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>18.5</v>
+        <v>22.9</v>
       </c>
       <c r="D516" t="n">
         <v>0</v>
@@ -11274,12 +11274,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Chermette Domaine du Vissoux Fleurie Poncié 2018</t>
+          <t>Emile Boeckel Pinot Gris Grand Cru Zotzenberg 2016</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -11295,16 +11295,16 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2013</t>
+          <t>David Duband Morey-Saint-Denis 2017</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>105</v>
+        <v>48.7</v>
       </c>
       <c r="D518" t="n">
         <v>0</v>
@@ -11316,16 +11316,16 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>François Bergeret Hautes Côtes de Beaune Rouge 2017</t>
+          <t>Château Tour Des Gendres Bergerac Blanc Moulin Des Dames 2016</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>11.8</v>
+        <v>19.8</v>
       </c>
       <c r="D519" t="n">
         <v>0</v>
@@ -11337,16 +11337,16 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Champagne Mailly Grand Cru Les Echansons 2007</t>
+          <t>Champagne Agrapart &amp;amp; Fils L'Avizoise Extra Brut Blanc de Blancs Grand Cru 2012</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D520" t="n">
         <v>0</v>
@@ -11358,16 +11358,16 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Gewurztraminer Grand Cru Rangen De Thann Clos Saint-Urbain 2013</t>
+          <t>Champagne Agrapart &amp;amp; Fils Terroirs Brut Blanc de Blancs Grand Cru</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>77.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="D521" t="n">
         <v>0</v>
@@ -11379,16 +11379,16 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Domaine Pellé Menetou Salon Rouge Morogues 2017</t>
+          <t>Lucien Boillot Gevrey Chambertin Les Evocelles 2017</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>17.8</v>
+        <v>52.6</v>
       </c>
       <c r="D522" t="n">
         <v>0</v>
@@ -11400,16 +11400,16 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>David Duband Charmes-Chambertin Grand Cru 2014</t>
+          <t>Albert Mann Pinot Noir Grand P 2017</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>217.5</v>
+        <v>59.9</v>
       </c>
       <c r="D523" t="n">
         <v>0</v>
@@ -11421,16 +11421,16 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Kirsch d'Alsace Réserve Particulière</t>
+          <t>Albert Mann Pinot Noir Les Saintes Claires 2017</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
       <c r="D524" t="n">
         <v>0</v>
@@ -11442,16 +11442,16 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Domaine Schoenheitz Pinot Blanc Val Saint Grégoire 2017</t>
+          <t>Chili De Martino Gallardia Cinsault 2017</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>11.1</v>
+        <v>17.1</v>
       </c>
       <c r="D525" t="n">
         <v>0</v>
@@ -11463,16 +11463,16 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>David Duband Morey-Saint-Denis 1er Cru Les Broc 2016</t>
+          <t>Planeta Sicilia Plumbago 2017</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>64.90000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="D526" t="n">
         <v>0</v>
@@ -11484,16 +11484,16 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Cosse-Maisonneuve Cahors Le Sid 2014</t>
+          <t>Planeta Sicilia Noto Santa Cecilia 2016</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D527" t="n">
         <v>0</v>
@@ -11505,16 +11505,16 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Quetsch d'Alsace Réserve Particulière</t>
+          <t>I Fabbri Chianti Classico Terra Di Lamole 2015</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="D528" t="n">
         <v>0</v>
@@ -11526,16 +11526,16 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Liban Vallée de la Békaa Château Marsyas 2012</t>
+          <t>Alphonse Mellot Sancerre Rouge La Moussière 2014</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
       <c r="D529" t="n">
         <v>0</v>
@@ -11547,16 +11547,16 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Moulin de Gassac IGP Pays d'Hérault Guilhem Rouge 2019</t>
+          <t>Domaine Plageoles Vin de France Contre-Pied 2016</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>5.8</v>
+        <v>12.8</v>
       </c>
       <c r="D530" t="n">
         <v>0</v>
@@ -11568,16 +11568,16 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Maurice Schoech Riesling 2018</t>
+          <t>Clos du Mont-Olivet Lirac Rosé Farel 2019</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="D531" t="n">
         <v>0</v>
@@ -11589,16 +11589,16 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Jean-Paul Brun Beaujolais L'Ancien 2016</t>
+          <t>Camin Larredya Jurançon Moelleux Au Capcéu 2018</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>9.699999999999999</v>
+        <v>30</v>
       </c>
       <c r="D532" t="n">
         <v>0</v>
@@ -11610,16 +11610,16 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Maurice Schoech Riesling Grand Cru Rangen de Thann 2014</t>
+          <t>Château de Villeneuve Saumur-Champigny Le Grand Clos 2017</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>41.6</v>
+        <v>29.8</v>
       </c>
       <c r="D533" t="n">
         <v>0</v>
@@ -11631,16 +11631,16 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Marc Colin Et Fils Saint-Aubin Blanc Luce 2017</t>
+          <t>Maurice Schoech Riesling 2018</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>26.5</v>
+        <v>11.1</v>
       </c>
       <c r="D534" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>I Fabbri Chianti Classico Terra Di Lamole 2015</t>
+          <t>Domaine Clerget Echezeaux Grand Cru En Orveaux 2015</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>17.6</v>
+        <v>116.4</v>
       </c>
       <c r="D535" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Cave de Castelmaure Corbières Rouge Grande Cuvée 2017</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2016</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>12.8</v>
+        <v>121</v>
       </c>
       <c r="D536" t="n">
         <v>0</v>
@@ -11694,16 +11694,16 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Domaine Clerget Chambolle-Musigny 2014</t>
+          <t>Borie de Maurel Minervois Rouge Maxime 2003</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>42.1</v>
+        <v>45.9</v>
       </c>
       <c r="D537" t="n">
         <v>0</v>
@@ -11715,16 +11715,16 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Sancerre Rouge La Moussière 2014</t>
+          <t>Domaine de la Monardière Vacqueyras Blanc Galéjade 2018</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>30.6</v>
+        <v>24.4</v>
       </c>
       <c r="D538" t="n">
         <v>0</v>
@@ -11736,16 +11736,16 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Champagne Agrapart &amp;amp; Fils Terroirs Brut Blanc de Blancs Grand Cru</t>
+          <t>Chili De Martino Viejas Tinajas Cinsault 2013</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>62.1</v>
+        <v>24</v>
       </c>
       <c r="D539" t="n">
         <v>0</v>
@@ -11757,16 +11757,16 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Domaine Pellé Sancerre Rouge La Croix Au Garde 2017</t>
+          <t>Catherine et Claude Maréchal Savigny-Lès-Beaune Rouge 2017</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>19.8</v>
+        <v>35.6</v>
       </c>
       <c r="D540" t="n">
         <v>0</v>
@@ -11778,16 +11778,16 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny La Marginale 2017</t>
+          <t>Camin Larredya Jurançon Sec La Virada 2018</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>34.3</v>
+        <v>27.5</v>
       </c>
       <c r="D541" t="n">
         <v>0</v>
@@ -11799,16 +11799,16 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Decelle-Villa Marsannay Les Longeroies 2015</t>
+          <t>Decelle-Villa Beaune Rouge 2015</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>29.2</v>
+        <v>43.5</v>
       </c>
       <c r="D542" t="n">
         <v>0</v>
@@ -11820,16 +11820,16 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Emile Boeckel Pinot Gris Grand Cru Zotzenberg 2016</t>
+          <t>Thierry Germain Saumur-Champigny Clos de l'Echelier 2017</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>15.8</v>
+        <v>38</v>
       </c>
       <c r="D543" t="n">
         <v>0</v>
@@ -11841,16 +11841,16 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Rimauresq Côtes de Provence Rouge Cru Classé Quintessence 2015</t>
+          <t>Darnley's London Dry Gin Original</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D544" t="n">
         <v>0</v>
@@ -11862,16 +11862,16 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Lucien Boillot Pommard 1er Cru Les Croix Noires 2017</t>
+          <t>Domaine Giudicelli Vin de France Corail Rouge 2019</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>67</v>
+        <v>20.2</v>
       </c>
       <c r="D545" t="n">
         <v>0</v>
@@ -11883,16 +11883,16 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Maison Trimbach Riesling Grand Cru Schlossberg 2015</t>
+          <t>Domaine de La Tour Du Bon Bandol Rouge Saint Ferréol 2005</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>63.5</v>
+        <v>51</v>
       </c>
       <c r="D546" t="n">
         <v>0</v>
@@ -11904,16 +11904,16 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Albert Mann Pinot Noir Les Saintes Claires 2017</t>
+          <t>Domaine Jamet Côte Rôtie Fructus Voluptas 2018</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D547" t="n">
         <v>0</v>
@@ -11925,16 +11925,16 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>David Duband Morey-Saint-Denis 2017</t>
+          <t>Zind-Humbrecht Gewurztraminer Grand Cru Rangen De Thann Clos Saint-Urbain 2013</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>48.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D548" t="n">
         <v>0</v>
@@ -11946,16 +11946,16 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Antoine-Marie Arena Vin de France Bianco Gentile 2018</t>
+          <t>Pierre Jean Villa Saint-Joseph Saut De l'Ange 2018</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>25.9</v>
+        <v>34.3</v>
       </c>
       <c r="D549" t="n">
         <v>0</v>
@@ -11967,16 +11967,16 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Château Tour De Pez Saint-Estèphe Les Hauts de Pez 2016</t>
+          <t>Oratoire Saint Martin Cairanne Rouge Les Douyes 2016</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="D550" t="n">
         <v>0</v>
@@ -11988,16 +11988,16 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Château Simone Palette Rouge 2015</t>
+          <t>Gilles Robin Hermitage Rouge 2012</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>46.5</v>
+        <v>60</v>
       </c>
       <c r="D551" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Château de la Selve Coteaux de l'Ardèche Rouge Serre de Berty 2014</t>
+          <t>Planeta Sicilia Etna Rosso 2018</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="D552" t="n">
         <v>0</v>
@@ -12030,16 +12030,16 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Albert Boxler Riesling Grand Cru Sommerberg "D" 2018</t>
+          <t>Lucien Boillot Volnay 1er Cru Les Angles 2017</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>71.3</v>
+        <v>58.8</v>
       </c>
       <c r="D553" t="n">
         <v>0</v>
@@ -12051,16 +12051,16 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Jean-Paul Brun Saint-Amour 2017</t>
+          <t>Chermette Domaine du Vissoux Fleurie Poncié 2018</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="D554" t="n">
         <v>0</v>
@@ -12072,16 +12072,16 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Pierre Gaillard Condrieu 2018</t>
+          <t>Château de Cazeneuve Languedoc Blanc 2016</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>32.7</v>
+        <v>18.9</v>
       </c>
       <c r="D555" t="n">
         <v>0</v>
@@ -12093,16 +12093,16 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2014</t>
+          <t>Domaine Sérol Vin Mousseux Rosé Turbullent Méthode Ancestrale</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>105</v>
+        <v>12.9</v>
       </c>
       <c r="D556" t="n">
         <v>0</v>
@@ -12114,16 +12114,16 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Champagne Mailly Grand Cru Intemporelle Rosé 2009</t>
+          <t>Vincent Carême Vouvray Moelleux 2015</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D557" t="n">
         <v>0</v>
@@ -12135,16 +12135,16 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Emile Boeckel Pinot Noir Terres Rouges 2016</t>
+          <t>Domaine Pellé Menetou Salon Rouge Les Cris 2015</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>35</v>
+        <v>21.9</v>
       </c>
       <c r="D558" t="n">
         <v>0</v>
@@ -12156,16 +12156,16 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Peat Chimney</t>
+          <t>Saumaize-Michelin Pouilly-Fuissé Les Ronchevats 2018</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>49.5</v>
+        <v>27.9</v>
       </c>
       <c r="D559" t="n">
         <v>0</v>
@@ -12177,16 +12177,16 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Sancerre Rouge En Grands Champs 2012</t>
+          <t>Domaine Des Croix Corton Grand Cru Les Grèves 2017</t>
         </is>
       </c>
       <c r="C560" t="n">
-        <v>59</v>
+        <v>102.3</v>
       </c>
       <c r="D560" t="n">
         <v>0</v>
@@ -12198,16 +12198,16 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Domaine Muré Crémant d'Alsace Cuvée Prestige</t>
+          <t>Rimauresq Côtes de Provence Rouge Cru Classé Quintessence 2015</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>14.3</v>
+        <v>30</v>
       </c>
       <c r="D561" t="n">
         <v>0</v>
@@ -12219,16 +12219,16 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>La Préceptorie Côtes du Roussillon Blanc Coume Marie 2018</t>
+          <t>Champagne Larmandier-Bernier Grand Cru Vieilles Vignes du Levant 2008</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>13.5</v>
+        <v>77</v>
       </c>
       <c r="D562" t="n">
         <v>0</v>
@@ -12240,16 +12240,16 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Tempier Bandol Migoua 2017</t>
+          <t>Domaine Huet Vouvray Le Mont Moelleux Première Trie 2008</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>58</v>
+        <v>59.6</v>
       </c>
       <c r="D563" t="n">
         <v>0</v>
@@ -12261,16 +12261,16 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Marc de Muscat</t>
+          <t>Domaine Weinbach Gewurztraminer Grand Cru Furstentum SGN 2010 1/2</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>39.6</v>
+        <v>124.8</v>
       </c>
       <c r="D564" t="n">
         <v>0</v>
@@ -12282,16 +12282,16 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Château La Tour l'Aspic Pauillac 2014</t>
+          <t>Cognac Frapin Château de Fontpinot XO 1/2</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>26.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D565" t="n">
         <v>0</v>
@@ -12303,16 +12303,16 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Domaine de l'Hortus Val de Montferrand La Grande Cuvée Blanc 2018</t>
+          <t>Albert Boxler Pinot Gris Grand Cru Sommerberg "W" 2016</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>24</v>
+        <v>56.4</v>
       </c>
       <c r="D566" t="n">
         <v>0</v>
@@ -12324,16 +12324,16 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Mas de Daumas Gassac IGP Saint-Guilhem-le-Désert Blanc 2019</t>
+          <t>Maurel Pays d'Oc Cabernet-Sauvignon 2017</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>38</v>
+        <v>5.7</v>
       </c>
       <c r="D567" t="n">
         <v>0</v>
@@ -12345,16 +12345,16 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Parés Baltà Cava Brut Nature</t>
+          <t>Domaine Labranche Laffont Madiran Vieilles Vignes 2015</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>10.3</v>
+        <v>15.4</v>
       </c>
       <c r="D568" t="n">
         <v>0</v>
@@ -12366,16 +12366,16 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Domaine de l'Ecu Muscadet Taurus 2012</t>
+          <t>Albert Mann Pinot Gris Vendanges Tardives Altenbourg 2011</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>29.4</v>
+        <v>44</v>
       </c>
       <c r="D569" t="n">
         <v>0</v>
@@ -12387,16 +12387,16 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Tempier Bandol Tourtine 2017</t>
+          <t>Domaine de Montgilet Anjou Blanc 2016</t>
         </is>
       </c>
       <c r="C570" t="n">
-        <v>58</v>
+        <v>11.9</v>
       </c>
       <c r="D570" t="n">
         <v>0</v>
@@ -12408,16 +12408,16 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Domaine Sérol Côte Roannaise Les Originelles 2019</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2013</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>10.2</v>
+        <v>99</v>
       </c>
       <c r="D571" t="n">
         <v>0</v>
@@ -12429,16 +12429,16 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Sureau</t>
+          <t>Decelle-Villa Côte de Nuits Villages "Aux Montagnes" 2014</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>52.4</v>
+        <v>28.4</v>
       </c>
       <c r="D572" t="n">
         <v>0</v>
@@ -12450,16 +12450,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Outre Terre 2016</t>
+          <t>Antoine-Marie Arena Vin de France Bianco Gentile 2018</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>48.8</v>
+        <v>25.9</v>
       </c>
       <c r="D573" t="n">
         <v>0</v>
@@ -12471,16 +12471,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Domaine de l'Idylle Savoie Mondeuse Le Tithonien 2018</t>
+          <t>Château Simone Palette Rouge 2015</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>10.9</v>
+        <v>46.5</v>
       </c>
       <c r="D574" t="n">
         <v>0</v>
@@ -12492,16 +12492,16 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Domaine Clerget Chambolle-Musigny Les Charmes 2015</t>
+          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2007</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>73.3</v>
+        <v>54.8</v>
       </c>
       <c r="D575" t="n">
         <v>0</v>
@@ -12513,16 +12513,16 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Maurice Schoech Pinot Gris Grand Cru Schlossberg 2017</t>
+          <t>Champagne Agrapart &amp;amp; Fils Minéral Extra Brut Blanc de Blancs Grand Cru 2012</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>18.7</v>
+        <v>86.8</v>
       </c>
       <c r="D576" t="n">
         <v>0</v>
@@ -12534,16 +12534,16 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Wemyss Malts Single Cask Scotch Whisky Chai Caramel Latte 2002 Craigellachie</t>
+          <t>Thierry Germain Saumur-Champigny La Marginale 2017</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>114</v>
+        <v>34.3</v>
       </c>
       <c r="D577" t="n">
         <v>0</v>
@@ -12555,16 +12555,16 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Borie La Vitarèle Saint-Chinian Midi Rouge 2015</t>
+          <t>Château de Vaudieu Châteauneuf-du-Pape L'Avenue 2015</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>40.5</v>
+        <v>77.8</v>
       </c>
       <c r="D578" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Domaine Bulliat Moulin-à-Vent 2017</t>
+          <t>Le Pas de l'Escalette Terrasses du Larzac Le Grand Pas 2018</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>11.5</v>
+        <v>27.5</v>
       </c>
       <c r="D579" t="n">
         <v>0</v>
@@ -12597,16 +12597,16 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Jean-Batiste Arena Muscat du Cap Corse 2015</t>
+          <t>Domaine de l'Ecu Muscadet Taurus 2012</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="D580" t="n">
         <v>0</v>
@@ -12618,16 +12618,16 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>François Baur Riesling Grand Cru Brand Clos De La Treille 2017</t>
+          <t>Domaine de l'Ecu Muscadet Gneiss 2015</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>23.4</v>
+        <v>16.9</v>
       </c>
       <c r="D581" t="n">
         <v>0</v>
@@ -12639,16 +12639,16 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky The Hive Batch Strength</t>
+          <t>Château Saransot-Dupré Listrac-Médoc 2016</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>59</v>
+        <v>17.2</v>
       </c>
       <c r="D582" t="n">
         <v>0</v>
@@ -12660,16 +12660,16 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Château Tour De Pez Saint-Estèphe 2017</t>
+          <t>Marc Colin Et Fils Saint-Aubin Blanc Luce 2017</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>24</v>
+        <v>26.5</v>
       </c>
       <c r="D583" t="n">
         <v>0</v>
@@ -12681,16 +12681,16 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Domaine Labranche Laffont Madiran Tradition 2016</t>
+          <t>Saumaize-Michelin Saint-Véran Les Crèches 2018</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>8.699999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="D584" t="n">
         <v>0</v>
@@ -12702,16 +12702,16 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Domaine de l'Ecu Muscadet Gneiss 2015</t>
+          <t>Wemyss Malts Single Cask Scotch Whisky Choc 'n' Nut Pretzel 2001 Bunnahabhain</t>
         </is>
       </c>
       <c r="C585" t="n">
-        <v>16.9</v>
+        <v>122</v>
       </c>
       <c r="D585" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Kingsbarns Distillery Lowland Single Malt Whisky</t>
+          <t>Domaine de l'Idylle Savoie Mondeuse Le Tithonien 2018</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>57</v>
+        <v>10.9</v>
       </c>
       <c r="D586" t="n">
         <v>0</v>
@@ -12744,16 +12744,16 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Lucien Boillot Puligny-Montrachet 1er Cru Les Perrières 2016</t>
+          <t>Domaine Labranche Laffont Pacherenc du Vic-Bilh Sec 2017</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>83.7</v>
+        <v>12.7</v>
       </c>
       <c r="D587" t="n">
         <v>0</v>
@@ -12765,16 +12765,16 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Chili De Martino Viejas Tinajas Cinsault 2013</t>
+          <t>Cognac Frapin Château de Fontpinot 1989 20 Ans d'Age</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="D588" t="n">
         <v>0</v>
@@ -12786,16 +12786,16 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Borie La Vitarèle Saint-Chinian Les Crès 2016</t>
+          <t>Marcel Windholtz Eau de Vie de Marc de Muscat</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>21.4</v>
+        <v>39.6</v>
       </c>
       <c r="D589" t="n">
         <v>0</v>
@@ -12807,16 +12807,16 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Outre Terre 2017</t>
+          <t>David Duband Chambolle-Musigny 1er Cru Les Sentiers 2016</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>48.8</v>
+        <v>105.6</v>
       </c>
       <c r="D590" t="n">
         <v>0</v>
@@ -12828,16 +12828,16 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Maison Trimbach Riesling Cuvée Frédéric Emile 2012</t>
+          <t>Borie de Maurel Minervois Blanc La Belle Aude 2018</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>63.5</v>
+        <v>10.4</v>
       </c>
       <c r="D591" t="n">
         <v>0</v>
@@ -12849,16 +12849,16 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>François Baur Gewurztraminer Herrenweg de Turckheim 2016</t>
+          <t>Pierre Jean Villa Crozes-Hermitage Accroche Coeur 2018</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>13.7</v>
+        <v>20.8</v>
       </c>
       <c r="D592" t="n">
         <v>0</v>
@@ -12870,16 +12870,16 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Domaine des Bosquets Gigondas 2016</t>
+          <t>Thierry Germain Saumur-Champigny Franc De Pied 2016</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>22.9</v>
+        <v>36.2</v>
       </c>
       <c r="D593" t="n">
         <v>0</v>
@@ -12891,16 +12891,16 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Maison Trimbach Riesling 2017</t>
+          <t>Thierry Germain Saumur-Champigny Les Mémoires 2016</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>16.9</v>
+        <v>40.2</v>
       </c>
       <c r="D594" t="n">
         <v>0</v>
@@ -12912,16 +12912,16 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Château Tour Des Gendres Bergerac Blanc Moulin Des Dames 2016</t>
+          <t>Paul Ginglinger Riesling Drei Exa 2018</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="D595" t="n">
         <v>0</v>
@@ -12933,16 +12933,16 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2018</t>
+          <t>Emile Boeckel Pinot Noir Terres Rouges 2016</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>32.8</v>
+        <v>35</v>
       </c>
       <c r="D596" t="n">
         <v>0</v>
@@ -12954,16 +12954,16 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Tempier Bandol Blanc 2018</t>
+          <t>Moulin de Gassac IGP Pays d'Hérault Guilhem Rouge 2019</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>27.9</v>
+        <v>5.8</v>
       </c>
       <c r="D597" t="n">
         <v>0</v>
@@ -12975,16 +12975,16 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Pierre Jean Villa Saint-Joseph Rouge Tildé 2017</t>
+          <t>Jean-Paul Brun Beaujolais L'Ancien 2016</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>34.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D598" t="n">
         <v>0</v>
@@ -12996,16 +12996,16 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Domaine de Montgilet Anjou Blanc 2016</t>
+          <t>Jean-Paul Brun Saint-Amour 2017</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>11.9</v>
+        <v>14.5</v>
       </c>
       <c r="D599" t="n">
         <v>0</v>
@@ -13017,16 +13017,16 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Passito di Noto 2016</t>
+          <t>Domaine de Montgilet Vin de France Grolleau 2019</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>26.4</v>
+        <v>7.4</v>
       </c>
       <c r="D600" t="n">
         <v>0</v>
@@ -13038,16 +13038,16 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Le Vieux Donjon Châteauneuf-du-Pape 2013</t>
+          <t>Domaine de La Tour Du Bon Bandol Rouge Saint Ferréol 2018</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>37</v>
+        <v>39.1</v>
       </c>
       <c r="D601" t="n">
         <v>0</v>
@@ -13059,16 +13059,16 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge Reflets 2018</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Treacle Chest</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>16.9</v>
+        <v>59.8</v>
       </c>
       <c r="D602" t="n">
         <v>0</v>
@@ -13080,16 +13080,16 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Les Mémoires 2016</t>
+          <t>François Bergeret Hautes Côtes de Beaune Blanc 2018</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>40.2</v>
+        <v>13.1</v>
       </c>
       <c r="D603" t="n">
         <v>0</v>
@@ -13101,16 +13101,16 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Domaine de l'Ancienne Cure Bergerac Blanc Sec L'Abbaye 2016</t>
+          <t>Cave de Castelmaure Corbières Rouge Grande Cuvée 2017</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="D604" t="n">
         <v>0</v>
@@ -13122,16 +13122,16 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2016</t>
+          <t>Alphonse Mellot Sancerre Rouge En Grands Champs 2012</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="D605" t="n">
         <v>0</v>
@@ -13143,16 +13143,16 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Sancerre Rouge Génération XIX 2011</t>
+          <t>Marcel Windholtz Eau de Vie de Prunelle Sauvage</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>67.5</v>
+        <v>52.9</v>
       </c>
       <c r="D606" t="n">
         <v>0</v>
@@ -13164,16 +13164,16 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Château de Chantegrive Graves Blanc Caroline 2016</t>
+          <t>David Duband Nuits-Saint-Georges 2017</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>23</v>
+        <v>48.7</v>
       </c>
       <c r="D607" t="n">
         <v>0</v>
@@ -13185,16 +13185,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Champagne Mailly Grand Cru Brut Rosé</t>
+          <t>Argentine Alamos Catena Malbec 2017</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>37.5</v>
+        <v>19</v>
       </c>
       <c r="D608" t="n">
         <v>0</v>
@@ -13206,16 +13206,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>David Duband Chambolle-Musigny 1er Cru Les Sentiers 2016</t>
+          <t>Australie Harkham Wines Old Vines 2011</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>105.6</v>
+        <v>35.3</v>
       </c>
       <c r="D609" t="n">
         <v>0</v>
@@ -13227,16 +13227,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Domaine de l'Hortus Val de Montferrand La Bergerie Blanc 2018</t>
+          <t>Cosse-Maisonneuve Cahors Le Sid 2014</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>13.5</v>
+        <v>30.1</v>
       </c>
       <c r="D610" t="n">
         <v>0</v>
@@ -13248,16 +13248,16 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Champagne Agrapart &amp;amp; Fils Minéral Extra Brut Blanc de Blancs Grand Cru 2012</t>
+          <t>Domaine Muré Crémant d'Alsace Cuvée Prestige</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>86.8</v>
+        <v>14.3</v>
       </c>
       <c r="D611" t="n">
         <v>0</v>
@@ -13269,16 +13269,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Lucien Boillot Volnay 1er Cru Les Angles 2017</t>
+          <t>Maurice Schoech Pinot Gris Grand Cru Schlossberg 2017</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>58.8</v>
+        <v>18.7</v>
       </c>
       <c r="D612" t="n">
         <v>0</v>
@@ -13290,16 +13290,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Camin Larredya Jurançon Sec La Virada 2018</t>
+          <t>Domaine Chambeyron Vin de Pays des Collines Rhodaniennes Viognier 2016</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>27.5</v>
+        <v>12</v>
       </c>
       <c r="D613" t="n">
         <v>0</v>
@@ -13311,16 +13311,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Le Mont Moelleux Première Trie 2008</t>
+          <t>Thierry Germain Saumur Blanc Clos Roman 2016</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>59.6</v>
+        <v>57.7</v>
       </c>
       <c r="D614" t="n">
         <v>0</v>
@@ -13332,16 +13332,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Gilles Robin Hermitage Rouge 2012</t>
+          <t>Domaine Des Croix Beaune 1er Cru Les Cent Vignes 2017</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D615" t="n">
         <v>0</v>
@@ -13353,16 +13353,16 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois Pinot Noir Sous La Tour 2016</t>
+          <t>Domaine Des Croix Savigny-Lès-Beaune 1er Cru Les Peuillets 2015</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>35.1</v>
+        <v>46</v>
       </c>
       <c r="D616" t="n">
         <v>0</v>
@@ -13374,16 +13374,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Domaine de Montbourgeau Vin de Paille 2013</t>
+          <t>Camille Giroud Marsannay Rouge Les Longeroies 2016</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>17.7</v>
+        <v>33.6</v>
       </c>
       <c r="D617" t="n">
         <v>0</v>
@@ -13395,16 +13395,16 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Champagne Larmandier-Bernier Grand Cru Vieilles Vignes du Levant 2008</t>
+          <t>Château Monbrison Margaux Bouquet de Monbrison 2012</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="D618" t="n">
         <v>0</v>
@@ -13416,16 +13416,16 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Gratavinum Priorat GV5 2011</t>
+          <t>Stéphane Tissot Arbois Pinot Noir Sous La Tour 2016</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>42</v>
+        <v>35.1</v>
       </c>
       <c r="D619" t="n">
         <v>0</v>
@@ -13437,16 +13437,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Etna Bianco 2018</t>
+          <t>Domaine Peyre Rose Marlène N°3 2008</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>17.5</v>
+        <v>78</v>
       </c>
       <c r="D620" t="n">
         <v>0</v>
@@ -13458,16 +13458,16 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Domaine de Montbourgeau Côtes du Jura Poulsard 2018</t>
+          <t>Domaine de Vaccelli AOP Ajaccio Rouge Granit 174 2017</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>18.8</v>
+        <v>74.5</v>
       </c>
       <c r="D621" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Moulin de Gassac IGP Pays d'Hérault Rouge Mazet du Levant 2017</t>
+          <t>Domaine des Terres d'Ocre Saint-Pourçain Blanc Instant T 2018</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="D622" t="n">
         <v>0</v>
@@ -13500,16 +13500,16 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Lucien Boillot Nuits-Saint-Georges 1er Cru Les Pruliers 2017</t>
+          <t>Château de Villeneuve Saumur-Champigny Clos de la Bienboire 2018</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>79.8</v>
+        <v>13.4</v>
       </c>
       <c r="D623" t="n">
         <v>0</v>
@@ -13521,16 +13521,16 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Domaine Augustin Collioure Rouge Adéodat 2017</t>
+          <t>Château Peymartin Saint-Julien 2014</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>28</v>
+        <v>23.8</v>
       </c>
       <c r="D624" t="n">
         <v>0</v>
@@ -13542,16 +13542,16 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Gewurztraminer Clos Windsbuhl 2012</t>
+          <t>Stéphane Tissot Arbois D.D. 2016</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>56.3</v>
+        <v>18.25</v>
       </c>
       <c r="D625" t="n">
         <v>0</v>
@@ -13563,16 +13563,16 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Domaine Giudicelli Vin de France Corail Rouge 2019</t>
+          <t>Domaine de l'Ancienne Cure Bergerac Blanc Sec L'Abbaye 2016</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="D626" t="n">
         <v>0</v>
@@ -13584,16 +13584,16 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Châteauneuf-du-Pape 2007</t>
+          <t>Pierre Jean Villa Saint-Joseph Rouge Tildé 2017</t>
         </is>
       </c>
       <c r="C627" t="n">
-        <v>54.8</v>
+        <v>34.3</v>
       </c>
       <c r="D627" t="n">
         <v>0</v>
@@ -13605,16 +13605,16 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Oratoire Saint Martin Cairanne Blanc Réserve des Seigneurs 2018</t>
+          <t>Catherine et Claude Maréchal Pommard La Chanière 2017</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>12.9</v>
+        <v>50.4</v>
       </c>
       <c r="D628" t="n">
         <v>0</v>
@@ -13626,16 +13626,16 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Lucien Boillot Gevrey Chambertin 1er Cru Les Cherbaudes 2017</t>
+          <t>Château Simone Palette Blanc 2017</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>78</v>
+        <v>46.5</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
@@ -13647,16 +13647,16 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois Trousseau Singulier 2017</t>
+          <t>Paul Ginglinger Gewurztraminer Wahlenbourg 2017</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>27.3</v>
+        <v>13.7</v>
       </c>
       <c r="D630" t="n">
         <v>0</v>
@@ -13668,16 +13668,16 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Marc Colin Et Fils Chassagne-Montrachet Rouge Vieilles Vignes 2017</t>
+          <t>Domaine de l'Hortus Val de Montferrand La Bergerie Blanc 2018</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>26.5</v>
+        <v>13.5</v>
       </c>
       <c r="D631" t="n">
         <v>0</v>
@@ -13689,16 +13689,16 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Domaine Sérol Côte Roannaise Perdrizière 2016</t>
+          <t>Borie La Vitarèle Saint-Chinian Les Crès 2016</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>16.6</v>
+        <v>21.4</v>
       </c>
       <c r="D632" t="n">
         <v>0</v>
@@ -13710,16 +13710,16 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Scotch Whisky Lord Elcho</t>
+          <t>Lucien Boillot Nuits-Saint-Georges 1er Cru Les Pruliers 2017</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>27.5</v>
+        <v>79.8</v>
       </c>
       <c r="D633" t="n">
         <v>0</v>
@@ -13731,16 +13731,16 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Rimauresq Côtes de Provence Blanc Cru Classé "R" 2019</t>
+          <t>Mérieau Touraine L'Arpent des Vaudons 2018</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="D634" t="n">
         <v>0</v>
@@ -13752,16 +13752,16 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2016</t>
+          <t>Château de Meursault Beaune-Grèves Les Trois Journaux 1er Cru 2015</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>121</v>
+        <v>67.2</v>
       </c>
       <c r="D635" t="n">
         <v>0</v>
@@ -13773,16 +13773,16 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Domaine Rotier Gaillac Blanc Doux Les Gravels 2016</t>
+          <t>Thierry Germain Saumur-Champigny La Marginale 2016</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>12.9</v>
+        <v>33.4</v>
       </c>
       <c r="D636" t="n">
         <v>0</v>
@@ -13794,16 +13794,16 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Weingut Besson-Strasser Zürich Räuschling 2018</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Vanilla Burst</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>33.2</v>
+        <v>57</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
@@ -13815,16 +13815,16 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Australie Maverick Breechens Blend 2012</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Peat Chimney Batch Strength</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>16.1</v>
+        <v>59</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
@@ -13836,16 +13836,16 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Rimauresq Côtes de Provence Rouge Cru Classé "R" 2017</t>
+          <t>Domaine Schoenheitz Pinot Gris Herrenreben 2017</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>23.2</v>
+        <v>18.6</v>
       </c>
       <c r="D639" t="n">
         <v>0</v>
@@ -13857,16 +13857,16 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Domaine Schoenheitz Pinot Gris Herrenreben 2017</t>
+          <t>Domaine Saint-Nicolas Fiefs Vendéens Rouge Cuvée Jacques 2016</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>18.6</v>
+        <v>24.3</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
@@ -13878,16 +13878,16 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Domaine des Comtes Lafon Volnay 1er Cru Champans 2013</t>
+          <t>Marcel Richaud Cairanne Rouge 2018</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>99</v>
+        <v>18.4</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
@@ -13899,16 +13899,16 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Oratoire Saint Martin Cairanne Rouge Les Douyes 2016</t>
+          <t>Catherine et Claude Maréchal Savigny-Lès-Beaune Rouge 2016</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>19.5</v>
+        <v>32.2</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
@@ -13920,16 +13920,16 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Domaine de l'Ecu Muscadet Granite 2018</t>
+          <t>Nouvelle-Zélande Marlborough Momo Sauvignon Blanc 2018</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -13941,16 +13941,16 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Domaine Weinbach Gewurztraminer Grand Cru Furstentum SGN 2010 1/2</t>
+          <t>François Bergeret Hautes Côtes de Beaune Rouge 2017</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>124.8</v>
+        <v>11.8</v>
       </c>
       <c r="D644" t="n">
         <v>0</v>
@@ -13962,16 +13962,16 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Maurice Schoech Riesling Vendanges Tardives 2017</t>
+          <t>David-Beaupère Juliénas La Bottière Vieilles Vignes 2018</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>28.5</v>
+        <v>17.9</v>
       </c>
       <c r="D645" t="n">
         <v>0</v>
@@ -13983,16 +13983,16 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>David-Beaupère Juliénas La Bottière Vieilles Vignes 2018</t>
+          <t>Marcel Windholtz Eau de Vie de Sureau</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>17.9</v>
+        <v>52.4</v>
       </c>
       <c r="D646" t="n">
         <v>0</v>
@@ -14004,16 +14004,16 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Haut-Lieu Demi-Sec 2015</t>
+          <t>Thierry Germain Saumur-Champigny Outre Terre 2016</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>26.9</v>
+        <v>48.8</v>
       </c>
       <c r="D647" t="n">
         <v>0</v>
@@ -14025,16 +14025,16 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Pinot Gris Clos Windsbuhl 2013</t>
+          <t>Domaine Pellé Menetou Salon Rouge Morogues 2017</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>71.5</v>
+        <v>17.8</v>
       </c>
       <c r="D648" t="n">
         <v>0</v>
@@ -14046,16 +14046,16 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Chili Valdivieso Merlot 2017</t>
+          <t>Domaine Schoenheitz Pinot Noir Val Saint Grégoire 2017</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>10.7</v>
+        <v>18.2</v>
       </c>
       <c r="D649" t="n">
         <v>0</v>
@@ -14067,16 +14067,16 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Cognac Normandin Mercier VFC</t>
+          <t>François Baur Riesling Grand Cru Brand Clos De La Treille 2017</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>59.9</v>
+        <v>23.4</v>
       </c>
       <c r="D650" t="n">
         <v>0</v>
@@ -14088,16 +14088,16 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Maurice Schoech Pinot Gris Vendanges Tardives 2015</t>
+          <t>Domaine Hauvette IGP Alpilles Dolia 2012</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>29.5</v>
+        <v>44.6</v>
       </c>
       <c r="D651" t="n">
         <v>0</v>
@@ -14109,16 +14109,16 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Borie de Maurel Minervois Blanc La Belle Aude 2018</t>
+          <t>Maurice Schoech Riesling Vendanges Tardives 2017</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>10.4</v>
+        <v>28.5</v>
       </c>
       <c r="D652" t="n">
         <v>0</v>
@@ -14130,16 +14130,16 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny La Marginale 2016</t>
+          <t>Château Fonréaud Bordeaux Blanc Le Cygne 2016</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>33.4</v>
+        <v>21.7</v>
       </c>
       <c r="D653" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>La Préceptorie Côtes du Roussillon Blanc Terres Nouvelles 2018</t>
+          <t>Alphonse Mellot Coteaux Charitois Rouge Les Pénitents 2015</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>19</v>
+        <v>22.9</v>
       </c>
       <c r="D654" t="n">
         <v>0</v>
@@ -14172,16 +14172,16 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Vanilla Burst</t>
+          <t>Château de Chantegrive Graves Blanc Caroline 2016</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D655" t="n">
         <v>0</v>
@@ -14193,16 +14193,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Decelle-Villa Beaune Rouge 2015</t>
+          <t>Oratoire Saint Martin Cairanne Blanc Réserve des Seigneurs 2018</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>43.5</v>
+        <v>12.9</v>
       </c>
       <c r="D656" t="n">
         <v>0</v>
@@ -14214,16 +14214,16 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Plateau des Chênes Lirac 2015</t>
+          <t>Maison Trimbach Riesling Cuvée Frédéric Emile 2012</t>
         </is>
       </c>
       <c r="C657" t="n">
-        <v>14.7</v>
+        <v>63.5</v>
       </c>
       <c r="D657" t="n">
         <v>0</v>
@@ -14235,16 +14235,16 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Pierre Gaillard Côtes-du-Rhône Blanc Les Gendrines 2018</t>
+          <t>Argentine Mendoza Alamos Torrontes 2017</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>18.3</v>
+        <v>11.1</v>
       </c>
       <c r="D658" t="n">
         <v>0</v>
@@ -14256,16 +14256,16 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Thierry Germain Saumur-Champigny Outre Terre 2013</t>
+          <t>Thevenet Quintaine Viré-Clessé La Bongran 2015</t>
         </is>
       </c>
       <c r="C659" t="n">
-        <v>43</v>
+        <v>24.7</v>
       </c>
       <c r="D659" t="n">
         <v>0</v>
@@ -14277,16 +14277,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Domaine Hauvette IGP Alpilles Dolia 2013</t>
+          <t>Maison Trimbach Riesling 2017</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>48.5</v>
+        <v>16.9</v>
       </c>
       <c r="D660" t="n">
         <v>0</v>
@@ -14298,16 +14298,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Clos du Prieur Terrasses du Larzac 2018</t>
+          <t>Stéphane Tissot Arbois Trousseau Singulier 2017</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>17.2</v>
+        <v>27.3</v>
       </c>
       <c r="D661" t="n">
         <v>0</v>
@@ -14319,16 +14319,16 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Pierre Jean Villa Crozes-Hermitage Accroche Coeur 2018</t>
+          <t>Domaine de Montbourgeau Côtes du Jura Poulsard 2018</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="D662" t="n">
         <v>0</v>
@@ -14340,16 +14340,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Zind-Humbrecht Riesling Clos Windsbuhl 2014</t>
+          <t>Gilles Robin Cornas 2016</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D663" t="n">
         <v>0</v>
@@ -14361,16 +14361,16 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Champagne Larmandier-Bernier Latitude</t>
+          <t>Zind-Humbrecht Pinot Gris Clos Windsbuhl 2013</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>39</v>
+        <v>71.5</v>
       </c>
       <c r="D664" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Lirac Rosé Farel 2019</t>
+          <t>Lucien Boillot Gevrey Chambertin 1er Cru Les Cherbaudes 2017</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>13.9</v>
+        <v>78</v>
       </c>
       <c r="D665" t="n">
         <v>0</v>
@@ -14403,16 +14403,16 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Domaine de La Tour Du Bon Bandol Blanc 2019</t>
+          <t>Le Pas de l'Escalette IGP Pays d'Hérault Les Clapas Blanc 2018</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>19</v>
+        <v>22.4</v>
       </c>
       <c r="D666" t="n">
         <v>0</v>
@@ -14424,16 +14424,16 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Domaine Rotier Gaillac Rouge Renaissance 2016</t>
+          <t>Decelle-Villa Chambolle-Musigny 2017</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>13.2</v>
+        <v>72</v>
       </c>
       <c r="D667" t="n">
         <v>0</v>
@@ -14445,16 +14445,16 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>David Duband Nuits-Saint-Georges 2017</t>
+          <t>Domino Romano Ribera del Duero RDR 2015</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>48.7</v>
+        <v>46.5</v>
       </c>
       <c r="D668" t="n">
         <v>0</v>
@@ -14466,16 +14466,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Argentine Alamos Catena Malbec 2017</t>
+          <t>Pierre Gaillard Condrieu 2018</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>19</v>
+        <v>32.7</v>
       </c>
       <c r="D669" t="n">
         <v>0</v>
@@ -14487,16 +14487,16 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Camille Giroud Santenay Rouge 1er Cru Clos Rousseau 2016</t>
+          <t>Decelle-Villa Marsannay Les Longeroies 2015</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>38.4</v>
+        <v>29.2</v>
       </c>
       <c r="D670" t="n">
         <v>0</v>
@@ -14508,16 +14508,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Château de Meursault Beaune-Grèves Les Trois Journaux 1er Cru 2015</t>
+          <t>Rimauresq Côtes de Provence Rouge Cru Classé "R" 2017</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>67.2</v>
+        <v>23.2</v>
       </c>
       <c r="D671" t="n">
         <v>0</v>
@@ -14529,16 +14529,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Le Pas de l'Escalette IGP Pays d'Hérault Les Clapas Blanc 2018</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky The Hive 12 ans</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>22.4</v>
+        <v>62</v>
       </c>
       <c r="D672" t="n">
         <v>0</v>
@@ -14550,16 +14550,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Paul Ginglinger Gewurztraminer Wahlenbourg 2017</t>
+          <t>Cognac Frapin 1270</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>13.7</v>
+        <v>44</v>
       </c>
       <c r="D673" t="n">
         <v>0</v>
@@ -14571,16 +14571,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Le Clos du Bourg Demi-Sec 2017</t>
+          <t>Domaine de l'Ecu Muscadet Granite 2018</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>34.7</v>
+        <v>17.1</v>
       </c>
       <c r="D674" t="n">
         <v>0</v>
@@ -14592,16 +14592,16 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Cognac Frapin Château de Fontpinot XO 1/2</t>
+          <t>Domaine Augustin Collioure Rouge Adéodat 2017</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>68.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="D675" t="n">
         <v>0</v>
@@ -14613,16 +14613,16 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Mas de Daumas Gassac IGP Saint-Guilhem-le-Désert 2018</t>
+          <t>Domaine Rotier Gaillac Blanc Sec Renaissance 2015</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>38</v>
+        <v>10.7</v>
       </c>
       <c r="D676" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Decelle-Villa Chambolle-Musigny 2017</t>
+          <t>Domaine Sérol Côte Roannaise Perdrizière 2016</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>72</v>
+        <v>16.6</v>
       </c>
       <c r="D677" t="n">
         <v>0</v>
@@ -14655,16 +14655,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Marc Colin Et Fils Chassagne-Montrachet Blanc Les Vide-Bourses 1er Cru 2016</t>
+          <t>Camin Larredya Jurançon Sec La Part Davant 2018</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>61.6</v>
+        <v>16.8</v>
       </c>
       <c r="D678" t="n">
         <v>0</v>
@@ -14676,16 +14676,16 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>François Bergeret Hautes Côtes de Beaune Blanc 2018</t>
+          <t>Saumaize-Michelin Pouilly-Fuissé Vignes Blanches 2018</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>13.1</v>
+        <v>25.3</v>
       </c>
       <c r="D679" t="n">
         <v>0</v>
@@ -14697,16 +14697,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Château Jean Faure Saint-Emilion Grand Cru 2015</t>
+          <t>Domaine des Comtes Lafon Volnay 1er Cru Santenots du Milieu 2014</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>50.5</v>
+        <v>105</v>
       </c>
       <c r="D680" t="n">
         <v>0</v>
@@ -14718,16 +14718,16 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Alphonse Mellot Coteaux Charitois Rouge Les Pénitents 2015</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky Peat Chimney</t>
         </is>
       </c>
       <c r="C681" t="n">
-        <v>22.9</v>
+        <v>49.5</v>
       </c>
       <c r="D681" t="n">
         <v>0</v>
@@ -14739,16 +14739,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Borie de Maurel Minervois Rouge Maxime 2003</t>
+          <t>Lucien Boillot Pommard 1er Cru Les Croix Noires 2017</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>45.9</v>
+        <v>67</v>
       </c>
       <c r="D682" t="n">
         <v>0</v>
@@ -14760,16 +14760,16 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Weingut Besson-Strasser Zürich Pinot Noir Albi 2016</t>
+          <t>Nouvelle-Zélande Marlborough Kim Crawford Sauvignon Blanc 2015</t>
         </is>
       </c>
       <c r="C683" t="n">
-        <v>47.2</v>
+        <v>19.5</v>
       </c>
       <c r="D683" t="n">
         <v>0</v>
@@ -14781,16 +14781,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Chili Errazuriz Cabernet Sauvignon 2016</t>
+          <t>Alphonse Mellot Sancerre Rouge Génération XIX 2011</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>12.7</v>
+        <v>67.5</v>
       </c>
       <c r="D684" t="n">
         <v>0</v>
@@ -14802,16 +14802,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Albert Mann Pinot Gris Vendanges Tardives Altenbourg 2011</t>
+          <t>Australie Maverick Breechens Blend 2012</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>44</v>
+        <v>16.1</v>
       </c>
       <c r="D685" t="n">
         <v>0</v>
@@ -14823,16 +14823,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Australie Harkham Wines Old Vines 2011</t>
+          <t>Philippe Alliet Chinon Rouge Coteau de Noiré 2016</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>35.3</v>
+        <v>31.7</v>
       </c>
       <c r="D686" t="n">
         <v>0</v>
@@ -14844,16 +14844,16 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Camin Larredya Jurançon Sec La Part Davant 2018</t>
+          <t>Domaine Clerget Chambolle-Musigny Les Charmes 2015</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>16.8</v>
+        <v>73.3</v>
       </c>
       <c r="D687" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Moulin de Gassac IGP Pays d'Hérault Guilhem Blanc 2017</t>
+          <t>Camille Giroud Clos de Vougeot 2016</t>
         </is>
       </c>
       <c r="C688" t="n">
-        <v>5.2</v>
+        <v>175</v>
       </c>
       <c r="D688" t="n">
         <v>0</v>
@@ -14886,16 +14886,16 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Huiles d'Olive Extra Vierge Planeta 3x 10cl</t>
+          <t>Jean-Paul Brun Beaujolais Le Ronsay 2016</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="D689" t="n">
         <v>0</v>
@@ -14907,16 +14907,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Jean-Paul Brun Beaujolais Le Ronsay 2016</t>
+          <t>Maurice Schoech Pinot Gris Vendanges Tardives 2015</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>7.4</v>
+        <v>29.5</v>
       </c>
       <c r="D690" t="n">
         <v>0</v>
@@ -14928,16 +14928,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Stéphane Tissot Arbois Trousseau Amphore 2017</t>
+          <t>Maurice Schoech Riesling Grand Cru Rangen de Thann 2014</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>40.7</v>
+        <v>41.6</v>
       </c>
       <c r="D691" t="n">
         <v>0</v>
@@ -14949,16 +14949,16 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Château de Vaudieu Châteauneuf-du-Pape L'Avenue 2015</t>
+          <t>Camille Giroud Santenay Rouge 1er Cru Clos Rousseau 2016</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>77.8</v>
+        <v>38.4</v>
       </c>
       <c r="D692" t="n">
         <v>0</v>
@@ -14970,16 +14970,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Nouvelle-Zélande Marlborough Momo Sauvignon Blanc 2018</t>
+          <t>Domaine Peyre Rose Clos des Cistes 2008</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D693" t="n">
         <v>0</v>
@@ -14991,16 +14991,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Marcel Windholtz Eau de Vie de Baie de Houx</t>
+          <t>Château Carbonnieux Graves Blanc 2017</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>76.8</v>
+        <v>40.2</v>
       </c>
       <c r="D694" t="n">
         <v>0</v>
@@ -15012,16 +15012,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Château Monbrison Margaux Bouquet de Monbrison 2012</t>
+          <t>Domaine de Montbourgeau Vin de Paille 2013</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>24</v>
+        <v>17.7</v>
       </c>
       <c r="D695" t="n">
         <v>0</v>
@@ -15033,16 +15033,16 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Nouvelle-Zélande Marlborough Kim Crawford Sauvignon Blanc 2015</t>
+          <t>Cognac Normandin Mercier VFC</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>19.5</v>
+        <v>59.9</v>
       </c>
       <c r="D696" t="n">
         <v>0</v>
@@ -15054,16 +15054,16 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Le Clos du Bourg Moelleux Première Trie 2008</t>
+          <t>Moulin de Gassac IGP Pays d'Hérault Guilhem Blanc 2017</t>
         </is>
       </c>
       <c r="C697" t="n">
-        <v>59.6</v>
+        <v>5.2</v>
       </c>
       <c r="D697" t="n">
         <v>0</v>
@@ -15075,16 +15075,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Domaine Weinbach Pinot Blanc 2017</t>
+          <t>Planeta Sicilia Passito di Noto 2016</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>18</v>
+        <v>26.4</v>
       </c>
       <c r="D698" t="n">
         <v>0</v>
@@ -15096,16 +15096,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>François Bergeret Hautes Côtes de Beaune Vieilles Vignes Rondo 2017</t>
+          <t>Champagne Larmandier-Bernier Terre de Vertus Premier Cru 2011</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>13.4</v>
+        <v>49.5</v>
       </c>
       <c r="D699" t="n">
         <v>0</v>
@@ -15117,16 +15117,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Château Fonréaud Bordeaux Blanc Le Cygne 2016</t>
+          <t>David Duband Morey-Saint-Denis 1er Cru Les Broc 2016</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>21.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D700" t="n">
         <v>0</v>
@@ -15138,16 +15138,16 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Domaine de Montgilet Vin de France Grolleau 2019</t>
+          <t>Weingut Besson-Strasser Zürich Räuschling 2018</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>7.4</v>
+        <v>33.2</v>
       </c>
       <c r="D701" t="n">
         <v>0</v>
@@ -15159,16 +15159,16 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Domaine Rouge Garance Côtes du Rhône Villages Garances 2016</t>
+          <t>Gratavinum Priorat GV5 2011</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="D702" t="n">
         <v>0</v>
@@ -15180,16 +15180,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Domaine Clerget Vosne-Romanée Les Violettes 2015</t>
+          <t>Zind-Humbrecht Pinot Gris Grand Cru Rangen De Thann Clos Saint-Urbain 2012</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>57</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D703" t="n">
         <v>0</v>
@@ -15201,16 +15201,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Domaine Huet Vouvray Haut-Lieu Sec 2017</t>
+          <t>Mas de Daumas Gassac IGP Saint-Guilhem-le-Désert Blanc 2019</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>24.4</v>
+        <v>38</v>
       </c>
       <c r="D704" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Clos du Mont-Olivet Vins de Pays du Gard Confluence 2017</t>
+          <t>Domaine Weinbach Pinot Blanc 2017</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="D705" t="n">
         <v>0</v>
@@ -15243,16 +15243,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Domaine La Croix Belle Côtes de Thongue Blanc Champ des Lys 2018</t>
+          <t>Domaine de Bellivière Jasnières Les Rosiers 2015</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>7.9</v>
+        <v>29.9</v>
       </c>
       <c r="D706" t="n">
         <v>0</v>
@@ -15264,16 +15264,16 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Domaine Chambeyron Vin de Pays des Collines Rhodaniennes Viognier 2016</t>
+          <t>Domaine de La Tour Du Bon Bandol Blanc 2019</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D707" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Domaine de Montcalmès Coteaux du Languedoc Blanc 2017</t>
+          <t>Wemyss Malts Blended Malt Scotch Whisky The Hive Batch Strength</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>28.5</v>
+        <v>59</v>
       </c>
       <c r="D708" t="n">
         <v>0</v>
@@ -15327,16 +15327,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Pierre Jean Villa Côte Rôtie Carmina 2017</t>
+          <t>Maison Trimbach Riesling Grand Cru Geisberg 2012</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>46</v>
+        <v>57.6</v>
       </c>
       <c r="D710" t="n">
         <v>0</v>
@@ -15348,16 +15348,16 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Wemyss Malts Blended Malt Scotch Whisky Peat Chimney Batch Strength</t>
+          <t>Clos du Prieur Terrasses du Larzac 2018</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>59</v>
+        <v>17.2</v>
       </c>
       <c r="D711" t="n">
         <v>0</v>
@@ -15369,16 +15369,16 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Domaine Sérol Vin Mousseux Rosé Turbullent Méthode Ancestrale</t>
+          <t>Marcel Windholtz Eau de Vie de Kirsch d'Alsace Réserve Particulière</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>12.9</v>
+        <v>62.4</v>
       </c>
       <c r="D712" t="n">
         <v>0</v>
@@ -15390,16 +15390,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Domino Romano Ribera del Duero RDR 2015</t>
+          <t>Planeta Sicilia Eruzione 1614 2017</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>46.5</v>
+        <v>23.5</v>
       </c>
       <c r="D713" t="n">
         <v>0</v>
@@ -15411,16 +15411,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Planeta Sicilia Plumbago 2017</t>
+          <t>Decelle-Villa Saint-Aubin 1er Cru Sous Roche Dumay 2015</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>11.6</v>
+        <v>44</v>
       </c>
       <c r="D714" t="n">
         <v>0</v>
@@ -15432,16 +15432,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Maurel Pays d'Oc Cabernet-Sauvignon 2017</t>
+          <t>Weingut Besson-Strasser Zürich Blauer Zweigelt 2016</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>5.7</v>
+        <v>32.2</v>
       </c>
       <c r="D715" t="n">
         <v>0</v>
